--- a/research/traditional_assets/database/data/south_africa/south_africa_retail_general.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_retail_general.xlsx
@@ -1418,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1555,22 +1555,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1259838414631684</v>
+        <v>0.1256765350912179</v>
       </c>
       <c r="C2">
-        <v>3884.449274418353</v>
+        <v>3859.118109327902</v>
       </c>
       <c r="D2">
-        <v>3757.949274418353</v>
+        <v>3772.407109327903</v>
       </c>
       <c r="E2">
-        <v>-992.4</v>
+        <v>-952.611</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39.789</v>
       </c>
       <c r="G2">
         <v>126.5</v>
@@ -1591,28 +1591,28 @@
         <v>382.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.0013867</v>
       </c>
       <c r="N2">
-        <v>382.3</v>
+        <v>380.2986132999999</v>
       </c>
       <c r="O2">
-        <v>103.221</v>
+        <v>102.680625591</v>
       </c>
       <c r="P2">
-        <v>279.079</v>
+        <v>277.617987709</v>
       </c>
       <c r="Q2">
-        <v>337.2789999999999</v>
+        <v>335.817987709</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1259838414631684</v>
+        <v>0.1265750960517353</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9676648369393251</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.0175579761772</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1637,22 +1637,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1256765350912179</v>
+        <v>0.1253692287192673</v>
       </c>
       <c r="C3">
-        <v>3859.118109327902</v>
+        <v>3833.898620192188</v>
       </c>
       <c r="D3">
-        <v>3772.407109327903</v>
+        <v>3786.976620192188</v>
       </c>
       <c r="E3">
-        <v>-952.611</v>
+        <v>-912.822</v>
       </c>
       <c r="F3">
-        <v>39.789</v>
+        <v>79.578</v>
       </c>
       <c r="G3">
         <v>126.5</v>
@@ -1673,28 +1673,28 @@
         <v>382.3</v>
       </c>
       <c r="M3">
-        <v>2.0013867</v>
+        <v>4.0027734</v>
       </c>
       <c r="N3">
-        <v>380.2986132999999</v>
+        <v>378.2972265999999</v>
       </c>
       <c r="O3">
-        <v>102.680625591</v>
+        <v>102.140251182</v>
       </c>
       <c r="P3">
-        <v>277.617987709</v>
+        <v>276.1569754179999</v>
       </c>
       <c r="Q3">
-        <v>335.817987709</v>
+        <v>334.3569754179999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1265750960517353</v>
+        <v>0.1271784170604769</v>
       </c>
       <c r="T3">
-        <v>0.9676648369393251</v>
+        <v>0.9748924671630281</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.0175579761772</v>
+        <v>95.50877898808859</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1719,22 +1719,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1253692287192673</v>
+        <v>0.1250619223473168</v>
       </c>
       <c r="C4">
-        <v>3833.898620192188</v>
+        <v>3808.792105947621</v>
       </c>
       <c r="D4">
-        <v>3786.976620192188</v>
+        <v>3801.659105947621</v>
       </c>
       <c r="E4">
-        <v>-912.822</v>
+        <v>-873.033</v>
       </c>
       <c r="F4">
-        <v>79.578</v>
+        <v>119.367</v>
       </c>
       <c r="G4">
         <v>126.5</v>
@@ -1755,28 +1755,28 @@
         <v>382.3</v>
       </c>
       <c r="M4">
-        <v>4.0027734</v>
+        <v>6.0041601</v>
       </c>
       <c r="N4">
-        <v>378.2972265999999</v>
+        <v>376.2958399</v>
       </c>
       <c r="O4">
-        <v>102.140251182</v>
+        <v>101.599876773</v>
       </c>
       <c r="P4">
-        <v>276.1569754179999</v>
+        <v>274.695963127</v>
       </c>
       <c r="Q4">
-        <v>334.3569754179999</v>
+        <v>332.895963127</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1271784170604769</v>
+        <v>0.1277941776776462</v>
       </c>
       <c r="T4">
-        <v>0.9748924671630281</v>
+        <v>0.9822691206903127</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.50877898808859</v>
+        <v>63.6725193253924</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1250619223473168</v>
+        <v>0.1247546159753662</v>
       </c>
       <c r="C5">
-        <v>3808.792105947621</v>
+        <v>3783.799885753453</v>
       </c>
       <c r="D5">
-        <v>3801.659105947621</v>
+        <v>3816.455885753453</v>
       </c>
       <c r="E5">
-        <v>-873.033</v>
+        <v>-833.2439999999999</v>
       </c>
       <c r="F5">
-        <v>119.367</v>
+        <v>159.156</v>
       </c>
       <c r="G5">
         <v>126.5</v>
@@ -1837,28 +1837,28 @@
         <v>382.3</v>
       </c>
       <c r="M5">
-        <v>6.0041601</v>
+        <v>8.005546799999999</v>
       </c>
       <c r="N5">
-        <v>376.2958399</v>
+        <v>374.2944532</v>
       </c>
       <c r="O5">
-        <v>101.599876773</v>
+        <v>101.059502364</v>
       </c>
       <c r="P5">
-        <v>274.695963127</v>
+        <v>273.2349508359999</v>
       </c>
       <c r="Q5">
-        <v>332.895963127</v>
+        <v>331.4349508359999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1277941776776462</v>
+        <v>0.1284227666410065</v>
       </c>
       <c r="T5">
-        <v>0.9822691206903127</v>
+        <v>0.9897994544994158</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.6725193253924</v>
+        <v>47.7543894940443</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1883,22 +1883,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1247546159753662</v>
+        <v>0.1244473096034156</v>
       </c>
       <c r="C6">
-        <v>3783.799885753453</v>
+        <v>3758.923299386855</v>
       </c>
       <c r="D6">
-        <v>3816.455885753453</v>
+        <v>3831.368299386855</v>
       </c>
       <c r="E6">
-        <v>-833.2439999999999</v>
+        <v>-793.4549999999999</v>
       </c>
       <c r="F6">
-        <v>159.156</v>
+        <v>198.945</v>
       </c>
       <c r="G6">
         <v>126.5</v>
@@ -1919,28 +1919,28 @@
         <v>382.3</v>
       </c>
       <c r="M6">
-        <v>8.005546799999999</v>
+        <v>10.0069335</v>
       </c>
       <c r="N6">
-        <v>374.2944532</v>
+        <v>372.2930665</v>
       </c>
       <c r="O6">
-        <v>101.059502364</v>
+        <v>100.519127955</v>
       </c>
       <c r="P6">
-        <v>273.2349508359999</v>
+        <v>271.773938545</v>
       </c>
       <c r="Q6">
-        <v>331.4349508359999</v>
+        <v>329.973938545</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1284227666410065</v>
+        <v>0.129064589056227</v>
       </c>
       <c r="T6">
-        <v>0.9897994544994158</v>
+        <v>0.9974883216518681</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.7543894940443</v>
+        <v>38.20351159523543</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1965,22 +1965,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1244473096034156</v>
+        <v>0.1241400032314651</v>
       </c>
       <c r="C7">
-        <v>3758.923299386855</v>
+        <v>3734.163707647307</v>
       </c>
       <c r="D7">
-        <v>3831.368299386855</v>
+        <v>3846.397707647307</v>
       </c>
       <c r="E7">
-        <v>-793.4549999999999</v>
+        <v>-753.6659999999999</v>
       </c>
       <c r="F7">
-        <v>198.945</v>
+        <v>238.734</v>
       </c>
       <c r="G7">
         <v>126.5</v>
@@ -2001,28 +2001,28 @@
         <v>382.3</v>
       </c>
       <c r="M7">
-        <v>10.0069335</v>
+        <v>12.0083202</v>
       </c>
       <c r="N7">
-        <v>372.2930665</v>
+        <v>370.2916797999999</v>
       </c>
       <c r="O7">
-        <v>100.519127955</v>
+        <v>99.97875354599999</v>
       </c>
       <c r="P7">
-        <v>271.773938545</v>
+        <v>270.3129262539999</v>
       </c>
       <c r="Q7">
-        <v>329.973938545</v>
+        <v>328.5129262539999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.129064589056227</v>
+        <v>0.1297200672675161</v>
       </c>
       <c r="T7">
-        <v>0.9974883216518681</v>
+        <v>1.005340781722458</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.20351159523543</v>
+        <v>31.83625966269619</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2047,22 +2047,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1241400032314651</v>
+        <v>0.1238326968595146</v>
       </c>
       <c r="C8">
-        <v>3734.163707647307</v>
+        <v>3709.522492770562</v>
       </c>
       <c r="D8">
-        <v>3846.397707647307</v>
+        <v>3861.545492770562</v>
       </c>
       <c r="E8">
-        <v>-753.6659999999999</v>
+        <v>-713.877</v>
       </c>
       <c r="F8">
-        <v>238.734</v>
+        <v>278.523</v>
       </c>
       <c r="G8">
         <v>126.5</v>
@@ -2083,28 +2083,28 @@
         <v>382.3</v>
       </c>
       <c r="M8">
-        <v>12.0083202</v>
+        <v>14.0097069</v>
       </c>
       <c r="N8">
-        <v>370.2916797999999</v>
+        <v>368.2902931</v>
       </c>
       <c r="O8">
-        <v>99.97875354599999</v>
+        <v>99.438379137</v>
       </c>
       <c r="P8">
-        <v>270.3129262539999</v>
+        <v>268.851913963</v>
       </c>
       <c r="Q8">
-        <v>328.5129262539999</v>
+        <v>327.051913963</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1297200672675161</v>
+        <v>0.1303896417844243</v>
       </c>
       <c r="T8">
-        <v>1.005340781722458</v>
+        <v>1.013362111902093</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.8362596626962</v>
+        <v>27.28822256802532</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2129,22 +2129,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1238326968595146</v>
+        <v>0.123525390487564</v>
       </c>
       <c r="C9">
-        <v>3709.522492770563</v>
+        <v>3685.001058852398</v>
       </c>
       <c r="D9">
-        <v>3861.545492770563</v>
+        <v>3876.813058852398</v>
       </c>
       <c r="E9">
-        <v>-713.877</v>
+        <v>-674.088</v>
       </c>
       <c r="F9">
-        <v>278.523</v>
+        <v>318.312</v>
       </c>
       <c r="G9">
         <v>126.5</v>
@@ -2165,28 +2165,28 @@
         <v>382.3</v>
       </c>
       <c r="M9">
-        <v>14.0097069</v>
+        <v>16.0110936</v>
       </c>
       <c r="N9">
-        <v>368.2902930999999</v>
+        <v>366.2889064</v>
       </c>
       <c r="O9">
-        <v>99.43837913699998</v>
+        <v>98.898004728</v>
       </c>
       <c r="P9">
-        <v>268.851913963</v>
+        <v>267.390901672</v>
       </c>
       <c r="Q9">
-        <v>327.0519139629999</v>
+        <v>325.590901672</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1303896417844243</v>
+        <v>0.1310737722690913</v>
       </c>
       <c r="T9">
-        <v>1.013362111902093</v>
+        <v>1.021557818824763</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.28822256802531</v>
+        <v>23.87719474702215</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.123525390487564</v>
+        <v>0.1232180841156135</v>
       </c>
       <c r="C10">
-        <v>3685.001058852398</v>
+        <v>3660.600832282483</v>
       </c>
       <c r="D10">
-        <v>3876.813058852398</v>
+        <v>3892.201832282483</v>
       </c>
       <c r="E10">
-        <v>-674.088</v>
+        <v>-634.299</v>
       </c>
       <c r="F10">
-        <v>318.312</v>
+        <v>358.101</v>
       </c>
       <c r="G10">
         <v>126.5</v>
@@ -2247,28 +2247,28 @@
         <v>382.3</v>
       </c>
       <c r="M10">
-        <v>16.0110936</v>
+        <v>18.0124803</v>
       </c>
       <c r="N10">
-        <v>366.2889064</v>
+        <v>364.2875197</v>
       </c>
       <c r="O10">
-        <v>98.898004728</v>
+        <v>98.35763031899999</v>
       </c>
       <c r="P10">
-        <v>267.390901672</v>
+        <v>265.929889381</v>
       </c>
       <c r="Q10">
-        <v>325.590901672</v>
+        <v>324.1298893809999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1310737722690913</v>
+        <v>0.1317729385885862</v>
       </c>
       <c r="T10">
-        <v>1.021557818824763</v>
+        <v>1.029933651174305</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.87719474702215</v>
+        <v>21.22417310846413</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2293,22 +2293,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1232180841156135</v>
+        <v>0.1229107777436629</v>
       </c>
       <c r="C11">
-        <v>3660.600832282483</v>
+        <v>3636.323262188613</v>
       </c>
       <c r="D11">
-        <v>3892.201832282483</v>
+        <v>3907.713262188613</v>
       </c>
       <c r="E11">
-        <v>-634.299</v>
+        <v>-594.51</v>
       </c>
       <c r="F11">
-        <v>358.101</v>
+        <v>397.89</v>
       </c>
       <c r="G11">
         <v>126.5</v>
@@ -2329,28 +2329,28 @@
         <v>382.3</v>
       </c>
       <c r="M11">
-        <v>18.0124803</v>
+        <v>20.013867</v>
       </c>
       <c r="N11">
-        <v>364.2875197</v>
+        <v>362.2861329999999</v>
       </c>
       <c r="O11">
-        <v>98.35763031899999</v>
+        <v>97.81725590999999</v>
       </c>
       <c r="P11">
-        <v>265.929889381</v>
+        <v>264.46887709</v>
       </c>
       <c r="Q11">
-        <v>324.1298893809999</v>
+        <v>322.66887709</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1317729385885862</v>
+        <v>0.1324876419374032</v>
       </c>
       <c r="T11">
-        <v>1.029933651174305</v>
+        <v>1.038495613131615</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.22417310846413</v>
+        <v>19.10175579761772</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2375,22 +2375,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1229107777436629</v>
+        <v>0.1226034713717123</v>
       </c>
       <c r="C12">
-        <v>3636.323262188613</v>
+        <v>3612.16982089161</v>
       </c>
       <c r="D12">
-        <v>3907.713262188613</v>
+        <v>3923.34882089161</v>
       </c>
       <c r="E12">
-        <v>-594.51</v>
+        <v>-554.721</v>
       </c>
       <c r="F12">
-        <v>397.89</v>
+        <v>437.679</v>
       </c>
       <c r="G12">
         <v>126.5</v>
@@ -2411,28 +2411,28 @@
         <v>382.3</v>
       </c>
       <c r="M12">
-        <v>20.013867</v>
+        <v>22.0152537</v>
       </c>
       <c r="N12">
-        <v>362.2861329999999</v>
+        <v>360.2847462999999</v>
       </c>
       <c r="O12">
-        <v>97.81725590999999</v>
+        <v>97.27688150099999</v>
       </c>
       <c r="P12">
-        <v>264.46887709</v>
+        <v>263.0078647989999</v>
       </c>
       <c r="Q12">
-        <v>322.66887709</v>
+        <v>321.2078647989999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1324876419374032</v>
+        <v>0.1332184060356318</v>
       </c>
       <c r="T12">
-        <v>1.038495613131615</v>
+        <v>1.047249978728415</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.10175579761772</v>
+        <v>17.36523254328884</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2457,22 +2457,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1226034713717123</v>
+        <v>0.1222961649997618</v>
       </c>
       <c r="C13">
-        <v>3612.16982089161</v>
+        <v>3588.142004371179</v>
       </c>
       <c r="D13">
-        <v>3923.34882089161</v>
+        <v>3939.110004371179</v>
       </c>
       <c r="E13">
-        <v>-554.721</v>
+        <v>-514.932</v>
       </c>
       <c r="F13">
-        <v>437.679</v>
+        <v>477.468</v>
       </c>
       <c r="G13">
         <v>126.5</v>
@@ -2493,28 +2493,28 @@
         <v>382.3</v>
       </c>
       <c r="M13">
-        <v>22.0152537</v>
+        <v>24.0166404</v>
       </c>
       <c r="N13">
-        <v>360.2847462999999</v>
+        <v>358.2833595999999</v>
       </c>
       <c r="O13">
-        <v>97.27688150099999</v>
+        <v>96.73650709199998</v>
       </c>
       <c r="P13">
-        <v>263.0078647989999</v>
+        <v>261.5468525079999</v>
       </c>
       <c r="Q13">
-        <v>321.2078647989999</v>
+        <v>319.7468525079999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1332184060356318</v>
+        <v>0.1339657784088202</v>
       </c>
       <c r="T13">
-        <v>1.047249978728415</v>
+        <v>1.056203307179687</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.36523254328884</v>
+        <v>15.9181298313481</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2539,22 +2539,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1222961649997618</v>
+        <v>0.1219888586278112</v>
       </c>
       <c r="C14">
-        <v>3588.142004371179</v>
+        <v>3564.24133274306</v>
       </c>
       <c r="D14">
-        <v>3939.110004371179</v>
+        <v>3954.99833274306</v>
       </c>
       <c r="E14">
-        <v>-514.932</v>
+        <v>-475.1429999999999</v>
       </c>
       <c r="F14">
-        <v>477.468</v>
+        <v>517.2570000000001</v>
       </c>
       <c r="G14">
         <v>126.5</v>
@@ -2575,28 +2575,28 @@
         <v>382.3</v>
       </c>
       <c r="M14">
-        <v>24.0166404</v>
+        <v>26.0180271</v>
       </c>
       <c r="N14">
-        <v>358.2833595999999</v>
+        <v>356.2819729</v>
       </c>
       <c r="O14">
-        <v>96.73650709199998</v>
+        <v>96.196132683</v>
       </c>
       <c r="P14">
-        <v>261.5468525079999</v>
+        <v>260.0858402169999</v>
       </c>
       <c r="Q14">
-        <v>319.7468525079999</v>
+        <v>318.2858402169999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1339657784088202</v>
+        <v>0.1347303317561049</v>
       </c>
       <c r="T14">
-        <v>1.056203307179687</v>
+        <v>1.065362459273518</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.9181298313481</v>
+        <v>14.69365830585978</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2621,22 +2621,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1219888586278112</v>
+        <v>0.1216815522558607</v>
       </c>
       <c r="C15">
-        <v>3564.24133274306</v>
+        <v>3540.469350747747</v>
       </c>
       <c r="D15">
-        <v>3954.99833274306</v>
+        <v>3971.015350747747</v>
       </c>
       <c r="E15">
-        <v>-475.1429999999999</v>
+        <v>-435.3539999999999</v>
       </c>
       <c r="F15">
-        <v>517.2570000000001</v>
+        <v>557.046</v>
       </c>
       <c r="G15">
         <v>126.5</v>
@@ -2657,28 +2657,28 @@
         <v>382.3</v>
       </c>
       <c r="M15">
-        <v>26.0180271</v>
+        <v>28.0194138</v>
       </c>
       <c r="N15">
-        <v>356.2819729</v>
+        <v>354.2805862</v>
       </c>
       <c r="O15">
-        <v>96.196132683</v>
+        <v>95.65575827399999</v>
       </c>
       <c r="P15">
-        <v>260.0858402169999</v>
+        <v>258.624827926</v>
       </c>
       <c r="Q15">
-        <v>318.2858402169999</v>
+        <v>316.824827926</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1347303317561049</v>
+        <v>0.1355126654137915</v>
       </c>
       <c r="T15">
-        <v>1.065362459273518</v>
+        <v>1.074734614904414</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.69365830585978</v>
+        <v>13.64411128401266</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2703,22 +2703,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1216815522558607</v>
+        <v>0.1215384958839101</v>
       </c>
       <c r="C16">
-        <v>3540.469350747747</v>
+        <v>3508.18088323665</v>
       </c>
       <c r="D16">
-        <v>3971.015350747747</v>
+        <v>3978.51588323665</v>
       </c>
       <c r="E16">
-        <v>-435.3539999999999</v>
+        <v>-395.5649999999998</v>
       </c>
       <c r="F16">
-        <v>557.046</v>
+        <v>596.8350000000002</v>
       </c>
       <c r="G16">
         <v>126.5</v>
@@ -2739,45 +2739,45 @@
         <v>382.3</v>
       </c>
       <c r="M16">
-        <v>28.0194138</v>
+        <v>30.91605300000001</v>
       </c>
       <c r="N16">
-        <v>354.2805862</v>
+        <v>351.3839469999999</v>
       </c>
       <c r="O16">
-        <v>95.65575827399999</v>
+        <v>94.87366568999998</v>
       </c>
       <c r="P16">
-        <v>258.624827926</v>
+        <v>256.5102813099999</v>
       </c>
       <c r="Q16">
-        <v>316.824827926</v>
+        <v>314.7102813099999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1355126654137915</v>
+        <v>0.1363134069222472</v>
       </c>
       <c r="T16">
-        <v>1.074734614904414</v>
+        <v>1.084327291844273</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.64411128401266</v>
+        <v>12.3657441006457</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2785,22 +2785,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1215384958839101</v>
+        <v>0.1212421395119596</v>
       </c>
       <c r="C17">
-        <v>3508.18088323665</v>
+        <v>3484.020529779963</v>
       </c>
       <c r="D17">
-        <v>3978.51588323665</v>
+        <v>3994.144529779963</v>
       </c>
       <c r="E17">
-        <v>-395.5649999999999</v>
+        <v>-355.776</v>
       </c>
       <c r="F17">
-        <v>596.835</v>
+        <v>636.624</v>
       </c>
       <c r="G17">
         <v>126.5</v>
@@ -2821,28 +2821,28 @@
         <v>382.3</v>
       </c>
       <c r="M17">
-        <v>30.916053</v>
+        <v>32.9771232</v>
       </c>
       <c r="N17">
-        <v>351.383947</v>
+        <v>349.3228768</v>
       </c>
       <c r="O17">
-        <v>94.87366569</v>
+        <v>94.31717673599999</v>
       </c>
       <c r="P17">
-        <v>256.51028131</v>
+        <v>255.005700064</v>
       </c>
       <c r="Q17">
-        <v>314.71028131</v>
+        <v>313.205700064</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1363134069222472</v>
+        <v>0.1371332137047138</v>
       </c>
       <c r="T17">
-        <v>1.084327291844273</v>
+        <v>1.094148365854128</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.3657441006457</v>
+        <v>11.59288509435535</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2867,22 +2867,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1212421395119596</v>
+        <v>0.120945783140009</v>
       </c>
       <c r="C18">
-        <v>3484.020529779963</v>
+        <v>3459.98344735179</v>
       </c>
       <c r="D18">
-        <v>3994.144529779963</v>
+        <v>4009.896447351789</v>
       </c>
       <c r="E18">
-        <v>-355.776</v>
+        <v>-315.987</v>
       </c>
       <c r="F18">
-        <v>636.624</v>
+        <v>676.413</v>
       </c>
       <c r="G18">
         <v>126.5</v>
@@ -2903,28 +2903,28 @@
         <v>382.3</v>
       </c>
       <c r="M18">
-        <v>32.9771232</v>
+        <v>35.0381934</v>
       </c>
       <c r="N18">
-        <v>349.3228768</v>
+        <v>347.2618065999999</v>
       </c>
       <c r="O18">
-        <v>94.31717673599999</v>
+        <v>93.76068778199999</v>
       </c>
       <c r="P18">
-        <v>255.005700064</v>
+        <v>253.501118818</v>
       </c>
       <c r="Q18">
-        <v>313.205700064</v>
+        <v>311.7011188179999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1371332137047138</v>
+        <v>0.1379727748674807</v>
       </c>
       <c r="T18">
-        <v>1.094148365854128</v>
+        <v>1.104206092249763</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.59288509435535</v>
+        <v>10.91095067704033</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2949,22 +2949,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.120945783140009</v>
+        <v>0.1206494267680584</v>
       </c>
       <c r="C19">
-        <v>3459.98344735179</v>
+        <v>3436.071100177965</v>
       </c>
       <c r="D19">
-        <v>4009.896447351789</v>
+        <v>4025.773100177964</v>
       </c>
       <c r="E19">
-        <v>-315.987</v>
+        <v>-276.1979999999999</v>
       </c>
       <c r="F19">
-        <v>676.413</v>
+        <v>716.2020000000001</v>
       </c>
       <c r="G19">
         <v>126.5</v>
@@ -2985,28 +2985,28 @@
         <v>382.3</v>
       </c>
       <c r="M19">
-        <v>35.0381934</v>
+        <v>37.09926360000001</v>
       </c>
       <c r="N19">
-        <v>347.2618065999999</v>
+        <v>345.2007363999999</v>
       </c>
       <c r="O19">
-        <v>93.76068778199999</v>
+        <v>93.20419882799999</v>
       </c>
       <c r="P19">
-        <v>253.501118818</v>
+        <v>251.9965375719999</v>
       </c>
       <c r="Q19">
-        <v>311.7011188179999</v>
+        <v>310.1965375719999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1379727748674807</v>
+        <v>0.1388328131317786</v>
       </c>
       <c r="T19">
-        <v>1.104206092249763</v>
+        <v>1.114509129045292</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.91095067704033</v>
+        <v>10.30478675053809</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3031,22 +3031,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1206494267680584</v>
+        <v>0.1205888603961079</v>
       </c>
       <c r="C20">
-        <v>3436.071100177963</v>
+        <v>3399.542297882306</v>
       </c>
       <c r="D20">
-        <v>4025.773100177963</v>
+        <v>4029.033297882307</v>
       </c>
       <c r="E20">
-        <v>-276.198</v>
+        <v>-236.409</v>
       </c>
       <c r="F20">
-        <v>716.202</v>
+        <v>755.991</v>
       </c>
       <c r="G20">
         <v>126.5</v>
@@ -3067,45 +3067,45 @@
         <v>382.3</v>
       </c>
       <c r="M20">
-        <v>37.0992636</v>
+        <v>40.4455185</v>
       </c>
       <c r="N20">
-        <v>345.2007364</v>
+        <v>341.8544815</v>
       </c>
       <c r="O20">
-        <v>93.204198828</v>
+        <v>92.300710005</v>
       </c>
       <c r="P20">
-        <v>251.996537572</v>
+        <v>249.553771495</v>
       </c>
       <c r="Q20">
-        <v>310.196537572</v>
+        <v>307.753771495</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1388328131317786</v>
+        <v>0.1397140869087752</v>
       </c>
       <c r="T20">
-        <v>1.114509129045292</v>
+        <v>1.12506656181108</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.30478675053809</v>
+        <v>9.452221511265828</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3113,22 +3113,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1205888603961079</v>
+        <v>0.1203049140241574</v>
       </c>
       <c r="C21">
-        <v>3399.542297882306</v>
+        <v>3375.108384219707</v>
       </c>
       <c r="D21">
-        <v>4029.033297882307</v>
+        <v>4044.388384219707</v>
       </c>
       <c r="E21">
-        <v>-236.409</v>
+        <v>-196.6199999999999</v>
       </c>
       <c r="F21">
-        <v>755.991</v>
+        <v>795.7800000000001</v>
       </c>
       <c r="G21">
         <v>126.5</v>
@@ -3149,28 +3149,28 @@
         <v>382.3</v>
       </c>
       <c r="M21">
-        <v>40.4455185</v>
+        <v>42.57423000000001</v>
       </c>
       <c r="N21">
-        <v>341.8544815</v>
+        <v>339.72577</v>
       </c>
       <c r="O21">
-        <v>92.300710005</v>
+        <v>91.7259579</v>
       </c>
       <c r="P21">
-        <v>249.553771495</v>
+        <v>247.9998121</v>
       </c>
       <c r="Q21">
-        <v>307.753771495</v>
+        <v>306.1998120999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1397140869087752</v>
+        <v>0.1406173925301967</v>
       </c>
       <c r="T21">
-        <v>1.12506656181108</v>
+        <v>1.135887930396014</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.452221511265828</v>
+        <v>8.979610435702533</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3195,22 +3195,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1203049140241574</v>
+        <v>0.1200209676522068</v>
       </c>
       <c r="C22">
-        <v>3375.108384219707</v>
+        <v>3350.791958140321</v>
       </c>
       <c r="D22">
-        <v>4044.388384219707</v>
+        <v>4059.860958140321</v>
       </c>
       <c r="E22">
-        <v>-196.6199999999999</v>
+        <v>-156.8309999999999</v>
       </c>
       <c r="F22">
-        <v>795.7800000000001</v>
+        <v>835.5690000000001</v>
       </c>
       <c r="G22">
         <v>126.5</v>
@@ -3231,28 +3231,28 @@
         <v>382.3</v>
       </c>
       <c r="M22">
-        <v>42.57423000000001</v>
+        <v>44.7029415</v>
       </c>
       <c r="N22">
-        <v>339.72577</v>
+        <v>337.5970584999999</v>
       </c>
       <c r="O22">
-        <v>91.7259579</v>
+        <v>91.151205795</v>
       </c>
       <c r="P22">
-        <v>247.9998121</v>
+        <v>246.4458527049999</v>
       </c>
       <c r="Q22">
-        <v>306.1998120999999</v>
+        <v>304.6458527049999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1406173925301967</v>
+        <v>0.141543566648363</v>
       </c>
       <c r="T22">
-        <v>1.135887930396014</v>
+        <v>1.1469832576793</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.979610435702533</v>
+        <v>8.552009938764318</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1200209676522068</v>
+        <v>0.1197370212802563</v>
       </c>
       <c r="C23">
-        <v>3350.791958140321</v>
+        <v>3326.594373235581</v>
       </c>
       <c r="D23">
-        <v>4059.860958140321</v>
+        <v>4075.452373235581</v>
       </c>
       <c r="E23">
-        <v>-156.831</v>
+        <v>-117.0419999999999</v>
       </c>
       <c r="F23">
-        <v>835.569</v>
+        <v>875.3580000000001</v>
       </c>
       <c r="G23">
         <v>126.5</v>
@@ -3313,28 +3313,28 @@
         <v>382.3</v>
       </c>
       <c r="M23">
-        <v>44.70294149999999</v>
+        <v>46.831653</v>
       </c>
       <c r="N23">
-        <v>337.5970584999999</v>
+        <v>335.4683469999999</v>
       </c>
       <c r="O23">
-        <v>91.151205795</v>
+        <v>90.57645368999999</v>
       </c>
       <c r="P23">
-        <v>246.4458527049999</v>
+        <v>244.8918933099999</v>
       </c>
       <c r="Q23">
-        <v>304.6458527049999</v>
+        <v>303.0918933099999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.141543566648363</v>
+        <v>0.1424934888208413</v>
       </c>
       <c r="T23">
-        <v>1.1469832576793</v>
+        <v>1.158363080533952</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.552009938764321</v>
+        <v>8.163282214275032</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3359,22 +3359,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1197370212802563</v>
+        <v>0.1194530749083057</v>
       </c>
       <c r="C24">
-        <v>3326.594373235581</v>
+        <v>3302.517003970325</v>
       </c>
       <c r="D24">
-        <v>4075.452373235581</v>
+        <v>4091.164003970325</v>
       </c>
       <c r="E24">
-        <v>-117.0419999999999</v>
+        <v>-77.25299999999993</v>
       </c>
       <c r="F24">
-        <v>875.3580000000001</v>
+        <v>915.147</v>
       </c>
       <c r="G24">
         <v>126.5</v>
@@ -3395,28 +3395,28 @@
         <v>382.3</v>
       </c>
       <c r="M24">
-        <v>46.831653</v>
+        <v>48.9603645</v>
       </c>
       <c r="N24">
-        <v>335.4683469999999</v>
+        <v>333.3396354999999</v>
       </c>
       <c r="O24">
-        <v>90.57645368999999</v>
+        <v>90.00170158499999</v>
       </c>
       <c r="P24">
-        <v>244.8918933099999</v>
+        <v>243.337933915</v>
       </c>
       <c r="Q24">
-        <v>303.0918933099999</v>
+        <v>301.5379339149999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1424934888208413</v>
+        <v>0.1434680842965009</v>
       </c>
       <c r="T24">
-        <v>1.158363080533952</v>
+        <v>1.17003848320301</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.163282214275032</v>
+        <v>7.808356900610899</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3441,22 +3441,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1194530749083057</v>
+        <v>0.1193092885363551</v>
       </c>
       <c r="C25">
-        <v>3302.517003970325</v>
+        <v>3270.730443402107</v>
       </c>
       <c r="D25">
-        <v>4091.164003970325</v>
+        <v>4099.166443402107</v>
       </c>
       <c r="E25">
-        <v>-77.25299999999993</v>
+        <v>-37.46399999999983</v>
       </c>
       <c r="F25">
-        <v>915.147</v>
+        <v>954.9360000000001</v>
       </c>
       <c r="G25">
         <v>126.5</v>
@@ -3477,45 +3477,45 @@
         <v>382.3</v>
       </c>
       <c r="M25">
-        <v>48.9603645</v>
+        <v>51.85302480000001</v>
       </c>
       <c r="N25">
-        <v>333.3396354999999</v>
+        <v>330.4469751999999</v>
       </c>
       <c r="O25">
-        <v>90.00170158499999</v>
+        <v>89.22068330399999</v>
       </c>
       <c r="P25">
-        <v>243.337933915</v>
+        <v>241.226291896</v>
       </c>
       <c r="Q25">
-        <v>301.5379339149999</v>
+        <v>299.426291896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1434680842965009</v>
+        <v>0.1444683270215199</v>
       </c>
       <c r="T25">
-        <v>1.17003848320301</v>
+        <v>1.182021133310729</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.808356900610899</v>
+        <v>7.372761791130841</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3523,22 +3523,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1193092885363551</v>
+        <v>0.1190311821644046</v>
       </c>
       <c r="C26">
-        <v>3270.730443402107</v>
+        <v>3246.508641334769</v>
       </c>
       <c r="D26">
-        <v>4099.166443402107</v>
+        <v>4114.733641334768</v>
       </c>
       <c r="E26">
-        <v>-37.46399999999994</v>
+        <v>2.325000000000045</v>
       </c>
       <c r="F26">
-        <v>954.936</v>
+        <v>994.725</v>
       </c>
       <c r="G26">
         <v>126.5</v>
@@ -3559,28 +3559,28 @@
         <v>382.3</v>
       </c>
       <c r="M26">
-        <v>51.8530248</v>
+        <v>54.0135675</v>
       </c>
       <c r="N26">
-        <v>330.4469751999999</v>
+        <v>328.2864324999999</v>
       </c>
       <c r="O26">
-        <v>89.22068330399999</v>
+        <v>88.63733677499999</v>
       </c>
       <c r="P26">
-        <v>241.226291896</v>
+        <v>239.6490957249999</v>
       </c>
       <c r="Q26">
-        <v>299.426291896</v>
+        <v>297.8490957249999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1444683270215199</v>
+        <v>0.1454952428858728</v>
       </c>
       <c r="T26">
-        <v>1.182021133310729</v>
+        <v>1.194323320754653</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.372761791130841</v>
+        <v>7.077851319485608</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3605,22 +3605,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1190311821644046</v>
+        <v>0.118753075792454</v>
       </c>
       <c r="C27">
-        <v>3246.508641334769</v>
+        <v>3222.405527530847</v>
       </c>
       <c r="D27">
-        <v>4114.733641334768</v>
+        <v>4130.419527530848</v>
       </c>
       <c r="E27">
-        <v>2.325000000000045</v>
+        <v>42.11400000000015</v>
       </c>
       <c r="F27">
-        <v>994.725</v>
+        <v>1034.514</v>
       </c>
       <c r="G27">
         <v>126.5</v>
@@ -3641,28 +3641,28 @@
         <v>382.3</v>
       </c>
       <c r="M27">
-        <v>54.0135675</v>
+        <v>56.17411020000001</v>
       </c>
       <c r="N27">
-        <v>328.2864324999999</v>
+        <v>326.1258897999999</v>
       </c>
       <c r="O27">
-        <v>88.63733677499999</v>
+        <v>88.05399024599998</v>
       </c>
       <c r="P27">
-        <v>239.6490957249999</v>
+        <v>238.0718995539999</v>
       </c>
       <c r="Q27">
-        <v>297.8490957249999</v>
+        <v>296.2718995539999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1454952428858728</v>
+        <v>0.146549913233046</v>
       </c>
       <c r="T27">
-        <v>1.194323320754653</v>
+        <v>1.206957999751115</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.077851319485608</v>
+        <v>6.805626268736161</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3687,22 +3687,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.118753075792454</v>
+        <v>0.1184749694205035</v>
       </c>
       <c r="C28">
-        <v>3222.405527530847</v>
+        <v>3198.422464548707</v>
       </c>
       <c r="D28">
-        <v>4130.419527530848</v>
+        <v>4146.225464548707</v>
       </c>
       <c r="E28">
-        <v>42.11400000000015</v>
+        <v>81.90300000000013</v>
       </c>
       <c r="F28">
-        <v>1034.514</v>
+        <v>1074.303</v>
       </c>
       <c r="G28">
         <v>126.5</v>
@@ -3723,28 +3723,28 @@
         <v>382.3</v>
       </c>
       <c r="M28">
-        <v>56.17411020000001</v>
+        <v>58.33465290000001</v>
       </c>
       <c r="N28">
-        <v>326.1258897999999</v>
+        <v>323.9653470999999</v>
       </c>
       <c r="O28">
-        <v>88.05399024599998</v>
+        <v>87.47064371699999</v>
       </c>
       <c r="P28">
-        <v>238.0718995539999</v>
+        <v>236.4947033829999</v>
       </c>
       <c r="Q28">
-        <v>296.2718995539999</v>
+        <v>294.6947033829999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.146549913233046</v>
+        <v>0.1476334786582239</v>
       </c>
       <c r="T28">
-        <v>1.206957999751115</v>
+        <v>1.219938834336522</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.805626268736161</v>
+        <v>6.553566036560746</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3769,22 +3769,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1184749694205035</v>
+        <v>0.1181968630485529</v>
       </c>
       <c r="C29">
-        <v>3198.422464548707</v>
+        <v>3174.56083588331</v>
       </c>
       <c r="D29">
-        <v>4146.225464548707</v>
+        <v>4162.15283588331</v>
       </c>
       <c r="E29">
-        <v>81.90300000000013</v>
+        <v>121.6920000000001</v>
       </c>
       <c r="F29">
-        <v>1074.303</v>
+        <v>1114.092</v>
       </c>
       <c r="G29">
         <v>126.5</v>
@@ -3805,28 +3805,28 @@
         <v>382.3</v>
       </c>
       <c r="M29">
-        <v>58.33465290000001</v>
+        <v>60.49519560000001</v>
       </c>
       <c r="N29">
-        <v>323.9653470999999</v>
+        <v>321.8048044</v>
       </c>
       <c r="O29">
-        <v>87.47064371699999</v>
+        <v>86.88729718799999</v>
       </c>
       <c r="P29">
-        <v>236.4947033829999</v>
+        <v>234.917507212</v>
       </c>
       <c r="Q29">
-        <v>294.6947033829999</v>
+        <v>293.117507212</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1476334786582239</v>
+        <v>0.1487471431229901</v>
       </c>
       <c r="T29">
-        <v>1.219938834336522</v>
+        <v>1.233280247660412</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.553566036560746</v>
+        <v>6.319510106683578</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3851,22 +3851,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1181968630485529</v>
+        <v>0.1181304566766024</v>
       </c>
       <c r="C30">
-        <v>3174.56083588331</v>
+        <v>3138.593095723691</v>
       </c>
       <c r="D30">
-        <v>4162.15283588331</v>
+        <v>4165.974095723691</v>
       </c>
       <c r="E30">
-        <v>121.6920000000001</v>
+        <v>161.4810000000001</v>
       </c>
       <c r="F30">
-        <v>1114.092</v>
+        <v>1153.881</v>
       </c>
       <c r="G30">
         <v>126.5</v>
@@ -3887,45 +3887,45 @@
         <v>382.3</v>
       </c>
       <c r="M30">
-        <v>60.49519560000001</v>
+        <v>63.80961930000001</v>
       </c>
       <c r="N30">
-        <v>321.8048044</v>
+        <v>318.4903806999999</v>
       </c>
       <c r="O30">
-        <v>86.88729718799999</v>
+        <v>85.992402789</v>
       </c>
       <c r="P30">
-        <v>234.917507212</v>
+        <v>232.497977911</v>
       </c>
       <c r="Q30">
-        <v>293.117507212</v>
+        <v>290.697977911</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1487471431229901</v>
+        <v>0.1498921784177498</v>
       </c>
       <c r="T30">
-        <v>1.233280247660412</v>
+        <v>1.24699747544413</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.319510106683578</v>
+        <v>5.991259690841</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3933,22 +3933,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1181304566766024</v>
+        <v>0.1178596503046518</v>
       </c>
       <c r="C31">
-        <v>3138.593095723691</v>
+        <v>3114.460185168106</v>
       </c>
       <c r="D31">
-        <v>4165.974095723691</v>
+        <v>4181.630185168106</v>
       </c>
       <c r="E31">
-        <v>161.4809999999999</v>
+        <v>201.2700000000001</v>
       </c>
       <c r="F31">
-        <v>1153.881</v>
+        <v>1193.67</v>
       </c>
       <c r="G31">
         <v>126.5</v>
@@ -3969,28 +3969,28 @@
         <v>382.3</v>
       </c>
       <c r="M31">
-        <v>63.80961929999999</v>
+        <v>66.009951</v>
       </c>
       <c r="N31">
-        <v>318.4903806999999</v>
+        <v>316.290049</v>
       </c>
       <c r="O31">
-        <v>85.992402789</v>
+        <v>85.39831323</v>
       </c>
       <c r="P31">
-        <v>232.497977911</v>
+        <v>230.89173577</v>
       </c>
       <c r="Q31">
-        <v>290.697977911</v>
+        <v>289.09173577</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1498921784177498</v>
+        <v>0.1510699290066454</v>
       </c>
       <c r="T31">
-        <v>1.24699747544413</v>
+        <v>1.261106624021669</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.991259690841001</v>
+        <v>5.791551034479634</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4015,22 +4015,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1178596503046518</v>
+        <v>0.1175888439327012</v>
       </c>
       <c r="C32">
-        <v>3114.460185168106</v>
+        <v>3090.445392374255</v>
       </c>
       <c r="D32">
-        <v>4181.630185168106</v>
+        <v>4197.404392374255</v>
       </c>
       <c r="E32">
-        <v>201.2700000000001</v>
+        <v>241.0590000000001</v>
       </c>
       <c r="F32">
-        <v>1193.67</v>
+        <v>1233.459</v>
       </c>
       <c r="G32">
         <v>126.5</v>
@@ -4051,28 +4051,28 @@
         <v>382.3</v>
       </c>
       <c r="M32">
-        <v>66.009951</v>
+        <v>68.21028270000001</v>
       </c>
       <c r="N32">
-        <v>316.290049</v>
+        <v>314.0897173</v>
       </c>
       <c r="O32">
-        <v>85.39831323</v>
+        <v>84.80422367099999</v>
       </c>
       <c r="P32">
-        <v>230.89173577</v>
+        <v>229.285493629</v>
       </c>
       <c r="Q32">
-        <v>289.09173577</v>
+        <v>287.485493629</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1510699290066454</v>
+        <v>0.1522818172937699</v>
       </c>
       <c r="T32">
-        <v>1.261106624021669</v>
+        <v>1.275624733427542</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.791551034479634</v>
+        <v>5.604726807560936</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4097,22 +4097,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1175888439327012</v>
+        <v>0.1173180375607507</v>
       </c>
       <c r="C33">
-        <v>3090.445392374255</v>
+        <v>3066.550059117315</v>
       </c>
       <c r="D33">
-        <v>4197.404392374255</v>
+        <v>4213.298059117315</v>
       </c>
       <c r="E33">
-        <v>241.0590000000001</v>
+        <v>280.8480000000001</v>
       </c>
       <c r="F33">
-        <v>1233.459</v>
+        <v>1273.248</v>
       </c>
       <c r="G33">
         <v>126.5</v>
@@ -4133,28 +4133,28 @@
         <v>382.3</v>
       </c>
       <c r="M33">
-        <v>68.21028270000001</v>
+        <v>70.4106144</v>
       </c>
       <c r="N33">
-        <v>314.0897173</v>
+        <v>311.8893856</v>
       </c>
       <c r="O33">
-        <v>84.80422367099999</v>
+        <v>84.21013411199999</v>
       </c>
       <c r="P33">
-        <v>229.285493629</v>
+        <v>227.679251488</v>
       </c>
       <c r="Q33">
-        <v>287.485493629</v>
+        <v>285.879251488</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1522818172937699</v>
+        <v>0.1535293493540451</v>
       </c>
       <c r="T33">
-        <v>1.275624733427542</v>
+        <v>1.290569846051235</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.604726807560936</v>
+        <v>5.429579094824657</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4179,22 +4179,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1173180375607507</v>
+        <v>0.1170472311888001</v>
       </c>
       <c r="C34">
-        <v>3066.550059117315</v>
+        <v>3042.775547572485</v>
       </c>
       <c r="D34">
-        <v>4213.298059117315</v>
+        <v>4229.312547572486</v>
       </c>
       <c r="E34">
-        <v>280.8480000000001</v>
+        <v>320.6370000000001</v>
       </c>
       <c r="F34">
-        <v>1273.248</v>
+        <v>1313.037</v>
       </c>
       <c r="G34">
         <v>126.5</v>
@@ -4215,28 +4215,28 @@
         <v>382.3</v>
       </c>
       <c r="M34">
-        <v>70.4106144</v>
+        <v>72.61094610000001</v>
       </c>
       <c r="N34">
-        <v>311.8893856</v>
+        <v>309.6890539</v>
       </c>
       <c r="O34">
-        <v>84.21013411199999</v>
+        <v>83.61604455299999</v>
       </c>
       <c r="P34">
-        <v>227.679251488</v>
+        <v>226.073009347</v>
       </c>
       <c r="Q34">
-        <v>285.879251488</v>
+        <v>284.273009347</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1535293493540451</v>
+        <v>0.1548141211773136</v>
       </c>
       <c r="T34">
-        <v>1.290569846051235</v>
+        <v>1.305961081439814</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.429579094824657</v>
+        <v>5.265046394981486</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4261,22 +4261,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1170472311888001</v>
+        <v>0.1167764248168496</v>
       </c>
       <c r="C35">
-        <v>3042.775547572485</v>
+        <v>3019.123240704163</v>
       </c>
       <c r="D35">
-        <v>4229.312547572486</v>
+        <v>4245.449240704163</v>
       </c>
       <c r="E35">
-        <v>320.6370000000001</v>
+        <v>360.426</v>
       </c>
       <c r="F35">
-        <v>1313.037</v>
+        <v>1352.826</v>
       </c>
       <c r="G35">
         <v>126.5</v>
@@ -4297,28 +4297,28 @@
         <v>382.3</v>
       </c>
       <c r="M35">
-        <v>72.61094610000001</v>
+        <v>74.8112778</v>
       </c>
       <c r="N35">
-        <v>309.6890539</v>
+        <v>307.4887222</v>
       </c>
       <c r="O35">
-        <v>83.61604455299999</v>
+        <v>83.021954994</v>
       </c>
       <c r="P35">
-        <v>226.073009347</v>
+        <v>224.466767206</v>
       </c>
       <c r="Q35">
-        <v>284.273009347</v>
+        <v>282.666767206</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1548141211773136</v>
+        <v>0.1561378254800751</v>
       </c>
       <c r="T35">
-        <v>1.305961081439814</v>
+        <v>1.321818717900775</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.265046394981486</v>
+        <v>5.110192089246737</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1167764248168496</v>
+        <v>0.116505618444899</v>
       </c>
       <c r="C36">
-        <v>3019.123240704163</v>
+        <v>2995.59454266406</v>
       </c>
       <c r="D36">
-        <v>4245.449240704163</v>
+        <v>4261.70954266406</v>
       </c>
       <c r="E36">
-        <v>360.426</v>
+        <v>400.2150000000003</v>
       </c>
       <c r="F36">
-        <v>1352.826</v>
+        <v>1392.615</v>
       </c>
       <c r="G36">
         <v>126.5</v>
@@ -4379,28 +4379,28 @@
         <v>382.3</v>
       </c>
       <c r="M36">
-        <v>74.8112778</v>
+        <v>77.01160950000002</v>
       </c>
       <c r="N36">
-        <v>307.4887222</v>
+        <v>305.2883904999999</v>
       </c>
       <c r="O36">
-        <v>83.021954994</v>
+        <v>82.42786543499999</v>
       </c>
       <c r="P36">
-        <v>224.466767206</v>
+        <v>222.8605250649999</v>
       </c>
       <c r="Q36">
-        <v>282.666767206</v>
+        <v>281.0605250649999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1561378254800751</v>
+        <v>0.1575022591459985</v>
       </c>
       <c r="T36">
-        <v>1.321818717900775</v>
+        <v>1.338164281637457</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.110192089246737</v>
+        <v>4.964186600982542</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4425,22 +4425,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.116505618444899</v>
+        <v>0.1162348120729485</v>
       </c>
       <c r="C37">
-        <v>2995.59454266406</v>
+        <v>2972.190879198507</v>
       </c>
       <c r="D37">
-        <v>4261.70954266406</v>
+        <v>4278.094879198507</v>
       </c>
       <c r="E37">
-        <v>400.2150000000003</v>
+        <v>440.0040000000002</v>
       </c>
       <c r="F37">
-        <v>1392.615</v>
+        <v>1432.404</v>
       </c>
       <c r="G37">
         <v>126.5</v>
@@ -4461,28 +4461,28 @@
         <v>382.3</v>
       </c>
       <c r="M37">
-        <v>77.01160950000002</v>
+        <v>79.21194120000001</v>
       </c>
       <c r="N37">
-        <v>305.2883904999999</v>
+        <v>303.0880587999999</v>
       </c>
       <c r="O37">
-        <v>82.42786543499999</v>
+        <v>81.83377587599999</v>
       </c>
       <c r="P37">
-        <v>222.8605250649999</v>
+        <v>221.2542829239999</v>
       </c>
       <c r="Q37">
-        <v>281.0605250649999</v>
+        <v>279.4542829239999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1575022591459985</v>
+        <v>0.158909331363982</v>
       </c>
       <c r="T37">
-        <v>1.338164281637457</v>
+        <v>1.355020644240911</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.964186600982542</v>
+        <v>4.826292528733028</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4507,22 +4507,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1162348120729485</v>
+        <v>0.1159640057009979</v>
       </c>
       <c r="C38">
-        <v>2972.190879198507</v>
+        <v>2948.913698065193</v>
       </c>
       <c r="D38">
-        <v>4278.094879198507</v>
+        <v>4294.606698065193</v>
       </c>
       <c r="E38">
-        <v>440.004</v>
+        <v>479.793</v>
       </c>
       <c r="F38">
-        <v>1432.404</v>
+        <v>1472.193</v>
       </c>
       <c r="G38">
         <v>126.5</v>
@@ -4543,28 +4543,28 @@
         <v>382.3</v>
       </c>
       <c r="M38">
-        <v>79.2119412</v>
+        <v>81.4122729</v>
       </c>
       <c r="N38">
-        <v>303.0880587999999</v>
+        <v>300.8877270999999</v>
       </c>
       <c r="O38">
-        <v>81.83377587599999</v>
+        <v>81.23968631699999</v>
       </c>
       <c r="P38">
-        <v>221.2542829239999</v>
+        <v>219.6480407829999</v>
       </c>
       <c r="Q38">
-        <v>279.4542829239999</v>
+        <v>277.8480407829999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.158909331363982</v>
+        <v>0.1603610725412665</v>
       </c>
       <c r="T38">
-        <v>1.355020644240911</v>
+        <v>1.372412129466696</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.826292528733028</v>
+        <v>4.695852190118622</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4589,22 +4589,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1159640057009979</v>
+        <v>0.1156931993290474</v>
       </c>
       <c r="C39">
-        <v>2948.913698065193</v>
+        <v>2925.76446945958</v>
       </c>
       <c r="D39">
-        <v>4294.606698065193</v>
+        <v>4311.24646945958</v>
       </c>
       <c r="E39">
-        <v>479.793</v>
+        <v>519.582</v>
       </c>
       <c r="F39">
-        <v>1472.193</v>
+        <v>1511.982</v>
       </c>
       <c r="G39">
         <v>126.5</v>
@@ -4625,28 +4625,28 @@
         <v>382.3</v>
       </c>
       <c r="M39">
-        <v>81.4122729</v>
+        <v>83.6126046</v>
       </c>
       <c r="N39">
-        <v>300.8877270999999</v>
+        <v>298.6873954</v>
       </c>
       <c r="O39">
-        <v>81.23968631699999</v>
+        <v>80.645596758</v>
       </c>
       <c r="P39">
-        <v>219.6480407829999</v>
+        <v>218.0417986419999</v>
       </c>
       <c r="Q39">
-        <v>277.8480407829999</v>
+        <v>276.2417986419999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1603610725412665</v>
+        <v>0.1618596440791086</v>
       </c>
       <c r="T39">
-        <v>1.372412129466696</v>
+        <v>1.390364630344926</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.695852190118622</v>
+        <v>4.572277132483922</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4671,22 +4671,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1156931993290474</v>
+        <v>0.1161341429570968</v>
       </c>
       <c r="C40">
-        <v>2925.76446945958</v>
+        <v>2858.947107703349</v>
       </c>
       <c r="D40">
-        <v>4311.24646945958</v>
+        <v>4284.218107703349</v>
       </c>
       <c r="E40">
-        <v>519.582</v>
+        <v>559.3710000000002</v>
       </c>
       <c r="F40">
-        <v>1511.982</v>
+        <v>1551.771</v>
       </c>
       <c r="G40">
         <v>126.5</v>
@@ -4707,45 +4707,45 @@
         <v>382.3</v>
       </c>
       <c r="M40">
-        <v>83.6126046</v>
+        <v>89.69236380000002</v>
       </c>
       <c r="N40">
-        <v>298.6873954</v>
+        <v>292.6076361999999</v>
       </c>
       <c r="O40">
-        <v>80.645596758</v>
+        <v>79.00406177399999</v>
       </c>
       <c r="P40">
-        <v>218.0417986419999</v>
+        <v>213.603574426</v>
       </c>
       <c r="Q40">
-        <v>276.2417986419999</v>
+        <v>271.803574426</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1618596440791086</v>
+        <v>0.1634073491099948</v>
       </c>
       <c r="T40">
-        <v>1.390364630344926</v>
+        <v>1.408905737809328</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.572277132483922</v>
+        <v>4.262347247893581</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4753,22 +4753,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1161341429570968</v>
+        <v>0.1158815865851463</v>
       </c>
       <c r="C41">
-        <v>2858.947107703349</v>
+        <v>2834.597349801724</v>
       </c>
       <c r="D41">
-        <v>4284.218107703349</v>
+        <v>4299.657349801724</v>
       </c>
       <c r="E41">
-        <v>559.3710000000002</v>
+        <v>599.1600000000002</v>
       </c>
       <c r="F41">
-        <v>1551.771</v>
+        <v>1591.56</v>
       </c>
       <c r="G41">
         <v>126.5</v>
@@ -4789,28 +4789,28 @@
         <v>382.3</v>
       </c>
       <c r="M41">
-        <v>89.69236380000002</v>
+        <v>91.99216800000002</v>
       </c>
       <c r="N41">
-        <v>292.6076361999999</v>
+        <v>290.307832</v>
       </c>
       <c r="O41">
-        <v>79.00406177399999</v>
+        <v>78.38311463999999</v>
       </c>
       <c r="P41">
-        <v>213.603574426</v>
+        <v>211.92471736</v>
       </c>
       <c r="Q41">
-        <v>271.803574426</v>
+        <v>270.12471736</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1634073491099948</v>
+        <v>0.1650066443085771</v>
       </c>
       <c r="T41">
-        <v>1.408905737809328</v>
+        <v>1.42806488218921</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.262347247893581</v>
+        <v>4.155788566696242</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4835,22 +4835,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1158815865851463</v>
+        <v>0.1156290302131957</v>
       </c>
       <c r="C42">
-        <v>2834.597349801724</v>
+        <v>2810.35927264257</v>
       </c>
       <c r="D42">
-        <v>4299.657349801724</v>
+        <v>4315.208272642571</v>
       </c>
       <c r="E42">
-        <v>599.1600000000002</v>
+        <v>638.9490000000002</v>
       </c>
       <c r="F42">
-        <v>1591.56</v>
+        <v>1631.349</v>
       </c>
       <c r="G42">
         <v>126.5</v>
@@ -4871,28 +4871,28 @@
         <v>382.3</v>
       </c>
       <c r="M42">
-        <v>91.99216800000002</v>
+        <v>94.29197220000002</v>
       </c>
       <c r="N42">
-        <v>290.307832</v>
+        <v>288.0080277999999</v>
       </c>
       <c r="O42">
-        <v>78.38311463999999</v>
+        <v>77.76216750599998</v>
       </c>
       <c r="P42">
-        <v>211.92471736</v>
+        <v>210.245860294</v>
       </c>
       <c r="Q42">
-        <v>270.12471736</v>
+        <v>268.4458602939999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1650066443085771</v>
+        <v>0.1666601529037215</v>
       </c>
       <c r="T42">
-        <v>1.42806488218921</v>
+        <v>1.447873489090443</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.155788566696242</v>
+        <v>4.054427869947553</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4917,22 +4917,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1156290302131957</v>
+        <v>0.1164495738412451</v>
       </c>
       <c r="C43">
-        <v>2810.35927264257</v>
+        <v>2720.452254099676</v>
       </c>
       <c r="D43">
-        <v>4315.208272642571</v>
+        <v>4265.090254099676</v>
       </c>
       <c r="E43">
-        <v>638.9490000000002</v>
+        <v>678.7380000000002</v>
       </c>
       <c r="F43">
-        <v>1631.349</v>
+        <v>1671.138</v>
       </c>
       <c r="G43">
         <v>126.5</v>
@@ -4953,45 +4953,45 @@
         <v>382.3</v>
       </c>
       <c r="M43">
-        <v>94.29197220000002</v>
+        <v>102.4407594</v>
       </c>
       <c r="N43">
-        <v>288.0080277999999</v>
+        <v>279.8592406</v>
       </c>
       <c r="O43">
-        <v>77.76216750599998</v>
+        <v>75.561994962</v>
       </c>
       <c r="P43">
-        <v>210.245860294</v>
+        <v>204.297245638</v>
       </c>
       <c r="Q43">
-        <v>268.4458602939999</v>
+        <v>262.497245638</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1666601529037215</v>
+        <v>0.1683706790366296</v>
       </c>
       <c r="T43">
-        <v>1.447873489090443</v>
+        <v>1.468365151402064</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.054427869947553</v>
+        <v>3.731912983065996</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4999,22 +4999,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1164495738412451</v>
+        <v>0.1162225674692946</v>
       </c>
       <c r="C44">
-        <v>2720.452254099677</v>
+        <v>2694.411725639669</v>
       </c>
       <c r="D44">
-        <v>4265.090254099677</v>
+        <v>4278.838725639669</v>
       </c>
       <c r="E44">
-        <v>678.7379999999999</v>
+        <v>718.5269999999999</v>
       </c>
       <c r="F44">
-        <v>1671.138</v>
+        <v>1710.927</v>
       </c>
       <c r="G44">
         <v>126.5</v>
@@ -5035,28 +5035,28 @@
         <v>382.3</v>
       </c>
       <c r="M44">
-        <v>102.4407594</v>
+        <v>104.8798251</v>
       </c>
       <c r="N44">
-        <v>279.8592406</v>
+        <v>277.4201748999999</v>
       </c>
       <c r="O44">
-        <v>75.561994962</v>
+        <v>74.90344722299999</v>
       </c>
       <c r="P44">
-        <v>204.297245638</v>
+        <v>202.5167276769999</v>
       </c>
       <c r="Q44">
-        <v>262.497245638</v>
+        <v>260.7167276769999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1683706790366295</v>
+        <v>0.1701412236303414</v>
       </c>
       <c r="T44">
-        <v>1.468365151402064</v>
+        <v>1.48957581940883</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.731912983065996</v>
+        <v>3.645124309041206</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5081,22 +5081,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1162225674692946</v>
+        <v>0.115995561097344</v>
       </c>
       <c r="C45">
-        <v>2694.411725639669</v>
+        <v>2668.460119914814</v>
       </c>
       <c r="D45">
-        <v>4278.838725639669</v>
+        <v>4292.676119914814</v>
       </c>
       <c r="E45">
-        <v>718.5269999999999</v>
+        <v>758.3160000000001</v>
       </c>
       <c r="F45">
-        <v>1710.927</v>
+        <v>1750.716</v>
       </c>
       <c r="G45">
         <v>126.5</v>
@@ -5117,28 +5117,28 @@
         <v>382.3</v>
       </c>
       <c r="M45">
-        <v>104.8798251</v>
+        <v>107.3188908</v>
       </c>
       <c r="N45">
-        <v>277.4201748999999</v>
+        <v>274.9811091999999</v>
       </c>
       <c r="O45">
-        <v>74.90344722299999</v>
+        <v>74.24489948399999</v>
       </c>
       <c r="P45">
-        <v>202.5167276769999</v>
+        <v>200.736209716</v>
       </c>
       <c r="Q45">
-        <v>260.7167276769999</v>
+        <v>258.936209716</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1701412236303414</v>
+        <v>0.1719750019595429</v>
       </c>
       <c r="T45">
-        <v>1.48957581940883</v>
+        <v>1.511544011272979</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.645124309041206</v>
+        <v>3.562280574744814</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5163,22 +5163,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.115995561097344</v>
+        <v>0.1166883547253935</v>
       </c>
       <c r="C46">
-        <v>2668.460119914814</v>
+        <v>2586.718690990805</v>
       </c>
       <c r="D46">
-        <v>4292.676119914814</v>
+        <v>4250.723690990805</v>
       </c>
       <c r="E46">
-        <v>758.3160000000001</v>
+        <v>798.1050000000001</v>
       </c>
       <c r="F46">
-        <v>1750.716</v>
+        <v>1790.505</v>
       </c>
       <c r="G46">
         <v>126.5</v>
@@ -5199,45 +5199,45 @@
         <v>382.3</v>
       </c>
       <c r="M46">
-        <v>107.3188908</v>
+        <v>114.7713705</v>
       </c>
       <c r="N46">
-        <v>274.9811091999999</v>
+        <v>267.5286295</v>
       </c>
       <c r="O46">
-        <v>74.24489948399999</v>
+        <v>72.23272996499999</v>
       </c>
       <c r="P46">
-        <v>200.736209716</v>
+        <v>195.295899535</v>
       </c>
       <c r="Q46">
-        <v>258.936209716</v>
+        <v>253.495899535</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1719750019595429</v>
+        <v>0.1738754631370791</v>
       </c>
       <c r="T46">
-        <v>1.511544011272979</v>
+        <v>1.534311046477644</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.562280574744814</v>
+        <v>3.330970069752717</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5245,22 +5245,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1166883547253935</v>
+        <v>0.1164817883534429</v>
       </c>
       <c r="C47">
-        <v>2586.718690990805</v>
+        <v>2559.352361546644</v>
       </c>
       <c r="D47">
-        <v>4250.723690990805</v>
+        <v>4263.146361546644</v>
       </c>
       <c r="E47">
-        <v>798.1050000000001</v>
+        <v>837.8940000000001</v>
       </c>
       <c r="F47">
-        <v>1790.505</v>
+        <v>1830.294</v>
       </c>
       <c r="G47">
         <v>126.5</v>
@@ -5281,28 +5281,28 @@
         <v>382.3</v>
       </c>
       <c r="M47">
-        <v>114.7713705</v>
+        <v>117.3218454</v>
       </c>
       <c r="N47">
-        <v>267.5286295</v>
+        <v>264.9781545999999</v>
       </c>
       <c r="O47">
-        <v>72.23272996499999</v>
+        <v>71.54410174199998</v>
       </c>
       <c r="P47">
-        <v>195.295899535</v>
+        <v>193.4340528579999</v>
       </c>
       <c r="Q47">
-        <v>253.495899535</v>
+        <v>251.6340528579999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1738754631370791</v>
+        <v>0.175846311765635</v>
       </c>
       <c r="T47">
-        <v>1.534311046477644</v>
+        <v>1.557921305208408</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.330970069752717</v>
+        <v>3.258557676932005</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5327,22 +5327,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1164817883534429</v>
+        <v>0.1162752219814924</v>
       </c>
       <c r="C48">
-        <v>2559.352361546644</v>
+        <v>2532.058855029872</v>
       </c>
       <c r="D48">
-        <v>4263.146361546644</v>
+        <v>4275.641855029872</v>
       </c>
       <c r="E48">
-        <v>837.8940000000001</v>
+        <v>877.6830000000001</v>
       </c>
       <c r="F48">
-        <v>1830.294</v>
+        <v>1870.083</v>
       </c>
       <c r="G48">
         <v>126.5</v>
@@ -5363,28 +5363,28 @@
         <v>382.3</v>
       </c>
       <c r="M48">
-        <v>117.3218454</v>
+        <v>119.8723203</v>
       </c>
       <c r="N48">
-        <v>264.9781545999999</v>
+        <v>262.4276796999999</v>
       </c>
       <c r="O48">
-        <v>71.54410174199998</v>
+        <v>70.85547351899999</v>
       </c>
       <c r="P48">
-        <v>193.4340528579999</v>
+        <v>191.572206181</v>
       </c>
       <c r="Q48">
-        <v>251.6340528579999</v>
+        <v>249.7722061809999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.175846311765635</v>
+        <v>0.1778915320405516</v>
       </c>
       <c r="T48">
-        <v>1.557921305208408</v>
+        <v>1.582422517098822</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.258557676932005</v>
+        <v>3.189226662529197</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1162752219814924</v>
+        <v>0.1160686556095418</v>
       </c>
       <c r="C49">
-        <v>2532.058855029872</v>
+        <v>2504.838813665727</v>
       </c>
       <c r="D49">
-        <v>4275.641855029872</v>
+        <v>4288.210813665727</v>
       </c>
       <c r="E49">
-        <v>877.6830000000001</v>
+        <v>917.4720000000003</v>
       </c>
       <c r="F49">
-        <v>1870.083</v>
+        <v>1909.872</v>
       </c>
       <c r="G49">
         <v>126.5</v>
@@ -5445,28 +5445,28 @@
         <v>382.3</v>
       </c>
       <c r="M49">
-        <v>119.8723203</v>
+        <v>122.4227952</v>
       </c>
       <c r="N49">
-        <v>262.4276796999999</v>
+        <v>259.8772048</v>
       </c>
       <c r="O49">
-        <v>70.85547351899999</v>
+        <v>70.16684529599999</v>
       </c>
       <c r="P49">
-        <v>191.572206181</v>
+        <v>189.710359504</v>
       </c>
       <c r="Q49">
-        <v>249.7722061809999</v>
+        <v>247.910359504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1778915320405516</v>
+        <v>0.1800154146337342</v>
       </c>
       <c r="T49">
-        <v>1.582422517098822</v>
+        <v>1.607866083292715</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5483,7 +5483,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.189226662529197</v>
+        <v>3.122784440393172</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5491,22 +5491,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1160686556095418</v>
+        <v>0.1158620892375913</v>
       </c>
       <c r="C50">
-        <v>2504.838813665727</v>
+        <v>2477.692887253416</v>
       </c>
       <c r="D50">
-        <v>4288.210813665727</v>
+        <v>4300.853887253416</v>
       </c>
       <c r="E50">
-        <v>917.4720000000001</v>
+        <v>957.2610000000001</v>
       </c>
       <c r="F50">
-        <v>1909.872</v>
+        <v>1949.661</v>
       </c>
       <c r="G50">
         <v>126.5</v>
@@ -5527,28 +5527,28 @@
         <v>382.3</v>
       </c>
       <c r="M50">
-        <v>122.4227952</v>
+        <v>124.9732701</v>
       </c>
       <c r="N50">
-        <v>259.8772048</v>
+        <v>257.3267298999999</v>
       </c>
       <c r="O50">
-        <v>70.16684529599999</v>
+        <v>69.47821707299998</v>
       </c>
       <c r="P50">
-        <v>189.710359504</v>
+        <v>187.8485128269999</v>
       </c>
       <c r="Q50">
-        <v>247.910359504</v>
+        <v>246.0485128269999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1800154146337342</v>
+        <v>0.182222586740375</v>
       </c>
       <c r="T50">
-        <v>1.607866083292715</v>
+        <v>1.634307436396171</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.122784440393172</v>
+        <v>3.05905414569127</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5573,22 +5573,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1158620892375913</v>
+        <v>0.1185025228656407</v>
       </c>
       <c r="C51">
-        <v>2477.692887253416</v>
+        <v>2281.704091350624</v>
       </c>
       <c r="D51">
-        <v>4300.853887253416</v>
+        <v>4144.654091350624</v>
       </c>
       <c r="E51">
-        <v>957.2610000000001</v>
+        <v>997.0500000000001</v>
       </c>
       <c r="F51">
-        <v>1949.661</v>
+        <v>1989.45</v>
       </c>
       <c r="G51">
         <v>126.5</v>
@@ -5609,45 +5609,45 @@
         <v>382.3</v>
       </c>
       <c r="M51">
-        <v>124.9732701</v>
+        <v>143.041455</v>
       </c>
       <c r="N51">
-        <v>257.3267298999999</v>
+        <v>239.2585449999999</v>
       </c>
       <c r="O51">
-        <v>69.47821707299998</v>
+        <v>64.59980714999999</v>
       </c>
       <c r="P51">
-        <v>187.8485128269999</v>
+        <v>174.65873785</v>
       </c>
       <c r="Q51">
-        <v>246.0485128269999</v>
+        <v>232.85873785</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.182222586740375</v>
+        <v>0.1845180457312814</v>
       </c>
       <c r="T51">
-        <v>1.634307436396171</v>
+        <v>1.661806443623766</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.05905414569127</v>
+        <v>2.672651784757083</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5655,22 +5655,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1185025228656407</v>
+        <v>0.1183528964936902</v>
       </c>
       <c r="C52">
-        <v>2281.704091350624</v>
+        <v>2250.462641960582</v>
       </c>
       <c r="D52">
-        <v>4144.654091350624</v>
+        <v>4153.201641960582</v>
       </c>
       <c r="E52">
-        <v>997.0500000000001</v>
+        <v>1036.839</v>
       </c>
       <c r="F52">
-        <v>1989.45</v>
+        <v>2029.239</v>
       </c>
       <c r="G52">
         <v>126.5</v>
@@ -5691,28 +5691,28 @@
         <v>382.3</v>
       </c>
       <c r="M52">
-        <v>143.041455</v>
+        <v>145.9022841</v>
       </c>
       <c r="N52">
-        <v>239.2585449999999</v>
+        <v>236.3977159</v>
       </c>
       <c r="O52">
-        <v>64.59980714999999</v>
+        <v>63.82738329299999</v>
       </c>
       <c r="P52">
-        <v>174.65873785</v>
+        <v>172.570332607</v>
       </c>
       <c r="Q52">
-        <v>232.85873785</v>
+        <v>230.7703326069999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1845180457312814</v>
+        <v>0.1869071969258983</v>
       </c>
       <c r="T52">
-        <v>1.661806443623766</v>
+        <v>1.69042785930963</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.672651784757083</v>
+        <v>2.620246847801062</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5737,22 +5737,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1183528964936902</v>
+        <v>0.1182032701217396</v>
       </c>
       <c r="C53">
-        <v>2250.462641960582</v>
+        <v>2219.256520781121</v>
       </c>
       <c r="D53">
-        <v>4153.201641960582</v>
+        <v>4161.784520781122</v>
       </c>
       <c r="E53">
-        <v>1036.839</v>
+        <v>1076.628</v>
       </c>
       <c r="F53">
-        <v>2029.239</v>
+        <v>2069.028</v>
       </c>
       <c r="G53">
         <v>126.5</v>
@@ -5773,28 +5773,28 @@
         <v>382.3</v>
       </c>
       <c r="M53">
-        <v>145.9022841</v>
+        <v>148.7631132</v>
       </c>
       <c r="N53">
-        <v>236.3977159</v>
+        <v>233.5368867999999</v>
       </c>
       <c r="O53">
-        <v>63.82738329299999</v>
+        <v>63.05495943599998</v>
       </c>
       <c r="P53">
-        <v>172.570332607</v>
+        <v>170.4819273639999</v>
       </c>
       <c r="Q53">
-        <v>230.7703326069999</v>
+        <v>228.6819273639999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1869071969258983</v>
+        <v>0.1893958960869575</v>
       </c>
       <c r="T53">
-        <v>1.69042785930963</v>
+        <v>1.720241833982405</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.620246847801062</v>
+        <v>2.569857485343348</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5819,22 +5819,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1182032701217396</v>
+        <v>0.1180536437497891</v>
       </c>
       <c r="C54">
-        <v>2219.256520781121</v>
+        <v>2188.085947290389</v>
       </c>
       <c r="D54">
-        <v>4161.784520781122</v>
+        <v>4170.402947290389</v>
       </c>
       <c r="E54">
-        <v>1076.628</v>
+        <v>1116.417</v>
       </c>
       <c r="F54">
-        <v>2069.028</v>
+        <v>2108.817</v>
       </c>
       <c r="G54">
         <v>126.5</v>
@@ -5855,28 +5855,28 @@
         <v>382.3</v>
       </c>
       <c r="M54">
-        <v>148.7631132</v>
+        <v>151.6239423</v>
       </c>
       <c r="N54">
-        <v>233.5368867999999</v>
+        <v>230.6760576999999</v>
       </c>
       <c r="O54">
-        <v>63.05495943599998</v>
+        <v>62.28253557899999</v>
       </c>
       <c r="P54">
-        <v>170.4819273639999</v>
+        <v>168.393522121</v>
       </c>
       <c r="Q54">
-        <v>228.6819273639999</v>
+        <v>226.5935221209999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1893958960869575</v>
+        <v>0.1919904973399767</v>
       </c>
       <c r="T54">
-        <v>1.720241833982405</v>
+        <v>1.75132448842849</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.569857485343348</v>
+        <v>2.521369608261399</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5901,22 +5901,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1180536437497891</v>
+        <v>0.1194413973778385</v>
       </c>
       <c r="C55">
-        <v>2188.085947290389</v>
+        <v>2069.706751739971</v>
       </c>
       <c r="D55">
-        <v>4170.402947290389</v>
+        <v>4091.812751739972</v>
       </c>
       <c r="E55">
-        <v>1116.417</v>
+        <v>1156.206</v>
       </c>
       <c r="F55">
-        <v>2108.817</v>
+        <v>2148.606</v>
       </c>
       <c r="G55">
         <v>126.5</v>
@@ -5937,45 +5937,45 @@
         <v>382.3</v>
       </c>
       <c r="M55">
-        <v>151.6239423</v>
+        <v>162.8643348</v>
       </c>
       <c r="N55">
-        <v>230.6760576999999</v>
+        <v>219.4356651999999</v>
       </c>
       <c r="O55">
-        <v>62.28253557899999</v>
+        <v>59.24762960399998</v>
       </c>
       <c r="P55">
-        <v>168.393522121</v>
+        <v>160.188035596</v>
       </c>
       <c r="Q55">
-        <v>226.5935221209999</v>
+        <v>218.388035596</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1919904973399767</v>
+        <v>0.1946979073431271</v>
       </c>
       <c r="T55">
-        <v>1.75132448842849</v>
+        <v>1.7837585626331</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.521369608261399</v>
+        <v>2.347352478794516</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5983,22 +5983,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1194413973778385</v>
+        <v>0.1193202410058879</v>
       </c>
       <c r="C56">
-        <v>2069.706751739971</v>
+        <v>2036.660781699056</v>
       </c>
       <c r="D56">
-        <v>4091.812751739972</v>
+        <v>4098.555781699057</v>
       </c>
       <c r="E56">
-        <v>1156.206</v>
+        <v>1195.995</v>
       </c>
       <c r="F56">
-        <v>2148.606</v>
+        <v>2188.395</v>
       </c>
       <c r="G56">
         <v>126.5</v>
@@ -6019,28 +6019,28 @@
         <v>382.3</v>
       </c>
       <c r="M56">
-        <v>162.8643348</v>
+        <v>165.880341</v>
       </c>
       <c r="N56">
-        <v>219.4356651999999</v>
+        <v>216.4196589999999</v>
       </c>
       <c r="O56">
-        <v>59.24762960399998</v>
+        <v>58.43330792999998</v>
       </c>
       <c r="P56">
-        <v>160.188035596</v>
+        <v>157.9863510699999</v>
       </c>
       <c r="Q56">
-        <v>218.388035596</v>
+        <v>216.1863510699999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1946979073431271</v>
+        <v>0.197525646679751</v>
       </c>
       <c r="T56">
-        <v>1.7837585626331</v>
+        <v>1.817634151246804</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.347352478794516</v>
+        <v>2.304673342816433</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6065,22 +6065,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1193202410058879</v>
+        <v>0.1191990846339374</v>
       </c>
       <c r="C57">
-        <v>2036.660781699056</v>
+        <v>2003.637072454713</v>
       </c>
       <c r="D57">
-        <v>4098.555781699057</v>
+        <v>4105.321072454713</v>
       </c>
       <c r="E57">
-        <v>1195.995</v>
+        <v>1235.784</v>
       </c>
       <c r="F57">
-        <v>2188.395</v>
+        <v>2228.184</v>
       </c>
       <c r="G57">
         <v>126.5</v>
@@ -6101,28 +6101,28 @@
         <v>382.3</v>
       </c>
       <c r="M57">
-        <v>165.880341</v>
+        <v>168.8963472</v>
       </c>
       <c r="N57">
-        <v>216.4196589999999</v>
+        <v>213.4036527999999</v>
       </c>
       <c r="O57">
-        <v>58.43330792999998</v>
+        <v>57.61898625599998</v>
       </c>
       <c r="P57">
-        <v>157.9863510699999</v>
+        <v>155.7846665439999</v>
       </c>
       <c r="Q57">
-        <v>216.1863510699999</v>
+        <v>213.9846665439999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.197525646679751</v>
+        <v>0.2004819196225849</v>
       </c>
       <c r="T57">
-        <v>1.817634151246804</v>
+        <v>1.853049539342949</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6139,7 +6139,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.304673342816433</v>
+        <v>2.263518461694711</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6147,22 +6147,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1191990846339374</v>
+        <v>0.1190779282619868</v>
       </c>
       <c r="C58">
-        <v>2003.637072454713</v>
+        <v>1970.63573442371</v>
       </c>
       <c r="D58">
-        <v>4105.321072454713</v>
+        <v>4112.10873442371</v>
       </c>
       <c r="E58">
-        <v>1235.784</v>
+        <v>1275.573</v>
       </c>
       <c r="F58">
-        <v>2228.184</v>
+        <v>2267.973</v>
       </c>
       <c r="G58">
         <v>126.5</v>
@@ -6183,28 +6183,28 @@
         <v>382.3</v>
       </c>
       <c r="M58">
-        <v>168.8963472</v>
+        <v>171.9123534000001</v>
       </c>
       <c r="N58">
-        <v>213.4036527999999</v>
+        <v>210.3876465999999</v>
       </c>
       <c r="O58">
-        <v>57.61898625599998</v>
+        <v>56.80466458199997</v>
       </c>
       <c r="P58">
-        <v>155.7846665439999</v>
+        <v>153.5829820179999</v>
       </c>
       <c r="Q58">
-        <v>213.9846665439999</v>
+        <v>211.7829820179999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2004819196225849</v>
+        <v>0.2035756936325275</v>
       </c>
       <c r="T58">
-        <v>1.853049539342949</v>
+        <v>1.890112154792403</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.263518461694711</v>
+        <v>2.223807611489541</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6229,22 +6229,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1190779282619868</v>
+        <v>0.1189567718900363</v>
       </c>
       <c r="C59">
-        <v>1970.63573442371</v>
+        <v>1937.65687875427</v>
       </c>
       <c r="D59">
-        <v>4112.10873442371</v>
+        <v>4118.91887875427</v>
       </c>
       <c r="E59">
-        <v>1275.573</v>
+        <v>1315.362</v>
       </c>
       <c r="F59">
-        <v>2267.973</v>
+        <v>2307.762</v>
       </c>
       <c r="G59">
         <v>126.5</v>
@@ -6265,28 +6265,28 @@
         <v>382.3</v>
       </c>
       <c r="M59">
-        <v>171.9123534000001</v>
+        <v>174.9283596</v>
       </c>
       <c r="N59">
-        <v>210.3876465999999</v>
+        <v>207.3716403999999</v>
       </c>
       <c r="O59">
-        <v>56.80466458199997</v>
+        <v>55.99034290799999</v>
       </c>
       <c r="P59">
-        <v>153.5829820179999</v>
+        <v>151.3812974919999</v>
       </c>
       <c r="Q59">
-        <v>211.7829820179999</v>
+        <v>209.5812974919999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2035756936325275</v>
+        <v>0.2068167902143721</v>
       </c>
       <c r="T59">
-        <v>1.890112154792403</v>
+        <v>1.928939656691832</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.223807611489541</v>
+        <v>2.185466100946618</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6311,22 +6311,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1189567718900363</v>
+        <v>0.1188356155180857</v>
       </c>
       <c r="C60">
-        <v>1937.656878754271</v>
+        <v>1904.700617332135</v>
       </c>
       <c r="D60">
-        <v>4118.918878754271</v>
+        <v>4125.751617332135</v>
       </c>
       <c r="E60">
-        <v>1315.362</v>
+        <v>1355.151</v>
       </c>
       <c r="F60">
-        <v>2307.762</v>
+        <v>2347.551</v>
       </c>
       <c r="G60">
         <v>126.5</v>
@@ -6347,28 +6347,28 @@
         <v>382.3</v>
       </c>
       <c r="M60">
-        <v>174.9283596</v>
+        <v>177.9443658</v>
       </c>
       <c r="N60">
-        <v>207.3716404</v>
+        <v>204.3556341999999</v>
       </c>
       <c r="O60">
-        <v>55.990342908</v>
+        <v>55.17602123399999</v>
       </c>
       <c r="P60">
-        <v>151.381297492</v>
+        <v>149.179612966</v>
       </c>
       <c r="Q60">
-        <v>209.5812974919999</v>
+        <v>207.3796129659999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.206816790214372</v>
+        <v>0.2102159890685017</v>
       </c>
       <c r="T60">
-        <v>1.928939656691831</v>
+        <v>1.969661183074158</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.185466100946619</v>
+        <v>2.148424302625489</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6393,22 +6393,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1188356155180857</v>
+        <v>0.1187144591461352</v>
       </c>
       <c r="C61">
-        <v>1904.700617332135</v>
+        <v>1871.767062786696</v>
       </c>
       <c r="D61">
-        <v>4125.751617332135</v>
+        <v>4132.607062786696</v>
       </c>
       <c r="E61">
-        <v>1355.151</v>
+        <v>1394.94</v>
       </c>
       <c r="F61">
-        <v>2347.551</v>
+        <v>2387.34</v>
       </c>
       <c r="G61">
         <v>126.5</v>
@@ -6429,28 +6429,28 @@
         <v>382.3</v>
       </c>
       <c r="M61">
-        <v>177.9443658</v>
+        <v>180.960372</v>
       </c>
       <c r="N61">
-        <v>204.3556341999999</v>
+        <v>201.3396279999999</v>
       </c>
       <c r="O61">
-        <v>55.17602123399999</v>
+        <v>54.36169955999998</v>
       </c>
       <c r="P61">
-        <v>149.179612966</v>
+        <v>146.9779284399999</v>
       </c>
       <c r="Q61">
-        <v>207.3796129659999</v>
+        <v>205.1779284399999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2102159890685017</v>
+        <v>0.2137851478653379</v>
       </c>
       <c r="T61">
-        <v>1.969661183074158</v>
+        <v>2.012418785775601</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.148424302625489</v>
+        <v>2.112617230915064</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1187144591461352</v>
+        <v>0.1185933027741846</v>
       </c>
       <c r="C62">
-        <v>1871.767062786696</v>
+        <v>1838.856328497179</v>
       </c>
       <c r="D62">
-        <v>4132.607062786696</v>
+        <v>4139.485328497179</v>
       </c>
       <c r="E62">
-        <v>1394.94</v>
+        <v>1434.729</v>
       </c>
       <c r="F62">
-        <v>2387.34</v>
+        <v>2427.129</v>
       </c>
       <c r="G62">
         <v>126.5</v>
@@ -6511,28 +6511,28 @@
         <v>382.3</v>
       </c>
       <c r="M62">
-        <v>180.960372</v>
+        <v>183.9763782</v>
       </c>
       <c r="N62">
-        <v>201.3396279999999</v>
+        <v>198.3236218</v>
       </c>
       <c r="O62">
-        <v>54.36169955999998</v>
+        <v>53.54737788599999</v>
       </c>
       <c r="P62">
-        <v>146.9779284399999</v>
+        <v>144.776243914</v>
       </c>
       <c r="Q62">
-        <v>205.1779284399999</v>
+        <v>202.976243914</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2137851478653379</v>
+        <v>0.2175373404466272</v>
       </c>
       <c r="T62">
-        <v>2.012418785775601</v>
+        <v>2.057369086051478</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.112617230915064</v>
+        <v>2.077984161555801</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6557,22 +6557,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1185933027741846</v>
+        <v>0.1184721464022341</v>
       </c>
       <c r="C63">
-        <v>1838.856328497179</v>
+        <v>1805.968528598898</v>
       </c>
       <c r="D63">
-        <v>4139.485328497179</v>
+        <v>4146.386528598898</v>
       </c>
       <c r="E63">
-        <v>1434.729</v>
+        <v>1474.518</v>
       </c>
       <c r="F63">
-        <v>2427.129</v>
+        <v>2466.918</v>
       </c>
       <c r="G63">
         <v>126.5</v>
@@ -6593,28 +6593,28 @@
         <v>382.3</v>
       </c>
       <c r="M63">
-        <v>183.9763782</v>
+        <v>186.9923844</v>
       </c>
       <c r="N63">
-        <v>198.3236218</v>
+        <v>195.3076155999999</v>
       </c>
       <c r="O63">
-        <v>53.54737788599999</v>
+        <v>52.73305621199999</v>
       </c>
       <c r="P63">
-        <v>144.776243914</v>
+        <v>142.574559388</v>
       </c>
       <c r="Q63">
-        <v>202.976243914</v>
+        <v>200.7745593879999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2175373404466272</v>
+        <v>0.2214870168479843</v>
       </c>
       <c r="T63">
-        <v>2.057369086051478</v>
+        <v>2.104685191605031</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.077984161555801</v>
+        <v>2.04446828798232</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6639,22 +6639,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1184721464022341</v>
+        <v>0.1183509900302835</v>
       </c>
       <c r="C64">
-        <v>1805.968528598898</v>
+        <v>1773.103777989567</v>
       </c>
       <c r="D64">
-        <v>4146.386528598898</v>
+        <v>4153.310777989567</v>
       </c>
       <c r="E64">
-        <v>1474.518</v>
+        <v>1514.307</v>
       </c>
       <c r="F64">
-        <v>2466.918</v>
+        <v>2506.707</v>
       </c>
       <c r="G64">
         <v>126.5</v>
@@ -6675,28 +6675,28 @@
         <v>382.3</v>
       </c>
       <c r="M64">
-        <v>186.9923844</v>
+        <v>190.0083906</v>
       </c>
       <c r="N64">
-        <v>195.3076155999999</v>
+        <v>192.2916093999999</v>
       </c>
       <c r="O64">
-        <v>52.73305621199999</v>
+        <v>51.91873453799999</v>
       </c>
       <c r="P64">
-        <v>142.574559388</v>
+        <v>140.3728748619999</v>
       </c>
       <c r="Q64">
-        <v>200.7745593879999</v>
+        <v>198.5728748619999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2214870168479843</v>
+        <v>0.2256501892710365</v>
       </c>
       <c r="T64">
-        <v>2.104685191605031</v>
+        <v>2.154558924485805</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.04446828798232</v>
+        <v>2.012016410395299</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6721,22 +6721,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1183509900302835</v>
+        <v>0.1248640736583329</v>
       </c>
       <c r="C65">
-        <v>1773.103777989567</v>
+        <v>1391.176317641286</v>
       </c>
       <c r="D65">
-        <v>4153.310777989567</v>
+        <v>3811.172317641286</v>
       </c>
       <c r="E65">
-        <v>1514.307</v>
+        <v>1554.096</v>
       </c>
       <c r="F65">
-        <v>2506.707</v>
+        <v>2546.496</v>
       </c>
       <c r="G65">
         <v>126.5</v>
@@ -6757,45 +6757,45 @@
         <v>382.3</v>
       </c>
       <c r="M65">
-        <v>190.0083906</v>
+        <v>229.18464</v>
       </c>
       <c r="N65">
-        <v>192.2916093999999</v>
+        <v>153.11536</v>
       </c>
       <c r="O65">
-        <v>51.91873453799999</v>
+        <v>41.34114719999999</v>
       </c>
       <c r="P65">
-        <v>140.3728748619999</v>
+        <v>111.7742128</v>
       </c>
       <c r="Q65">
-        <v>198.5728748619999</v>
+        <v>169.9742127999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2256501892710365</v>
+        <v>0.2300446490509248</v>
       </c>
       <c r="T65">
-        <v>2.154558924485805</v>
+        <v>2.207203420304399</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.012016410395299</v>
+        <v>1.668087355243353</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6803,22 +6803,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1248640736583329</v>
+        <v>0.1248465772863824</v>
       </c>
       <c r="C66">
-        <v>1391.176317641286</v>
+        <v>1352.230892287099</v>
       </c>
       <c r="D66">
-        <v>3811.172317641286</v>
+        <v>3812.015892287099</v>
       </c>
       <c r="E66">
-        <v>1554.096</v>
+        <v>1593.885</v>
       </c>
       <c r="F66">
-        <v>2546.496</v>
+        <v>2586.285</v>
       </c>
       <c r="G66">
         <v>126.5</v>
@@ -6839,28 +6839,28 @@
         <v>382.3</v>
       </c>
       <c r="M66">
-        <v>229.18464</v>
+        <v>232.76565</v>
       </c>
       <c r="N66">
-        <v>153.11536</v>
+        <v>149.5343499999999</v>
       </c>
       <c r="O66">
-        <v>41.34114719999999</v>
+        <v>40.37427449999998</v>
       </c>
       <c r="P66">
-        <v>111.7742128</v>
+        <v>109.1600754999999</v>
       </c>
       <c r="Q66">
-        <v>169.9742127999999</v>
+        <v>167.3600754999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2300446490509248</v>
+        <v>0.2346902208182354</v>
       </c>
       <c r="T66">
-        <v>2.207203420304399</v>
+        <v>2.262856173026912</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.668087355243353</v>
+        <v>1.642424472854993</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6885,22 +6885,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1248465772863824</v>
+        <v>0.1248290809144318</v>
       </c>
       <c r="C67">
-        <v>1352.230892287099</v>
+        <v>1313.285840453536</v>
       </c>
       <c r="D67">
-        <v>3812.015892287099</v>
+        <v>3812.859840453536</v>
       </c>
       <c r="E67">
-        <v>1593.885</v>
+        <v>1633.674</v>
       </c>
       <c r="F67">
-        <v>2586.285</v>
+        <v>2626.074</v>
       </c>
       <c r="G67">
         <v>126.5</v>
@@ -6921,28 +6921,28 @@
         <v>382.3</v>
       </c>
       <c r="M67">
-        <v>232.76565</v>
+        <v>236.34666</v>
       </c>
       <c r="N67">
-        <v>149.5343499999999</v>
+        <v>145.95334</v>
       </c>
       <c r="O67">
-        <v>40.37427449999998</v>
+        <v>39.4074018</v>
       </c>
       <c r="P67">
-        <v>109.1600754999999</v>
+        <v>106.5459382</v>
       </c>
       <c r="Q67">
-        <v>167.3600754999999</v>
+        <v>164.7459382</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2346902208182354</v>
+        <v>0.2396090615130348</v>
       </c>
       <c r="T67">
-        <v>2.262856173026912</v>
+        <v>2.321782617086044</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.642424472854993</v>
+        <v>1.617539253569312</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6967,22 +6967,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1248290809144318</v>
+        <v>0.1248115845424813</v>
       </c>
       <c r="C68">
-        <v>1313.285840453536</v>
+        <v>1274.341162388733</v>
       </c>
       <c r="D68">
-        <v>3812.859840453536</v>
+        <v>3813.704162388733</v>
       </c>
       <c r="E68">
-        <v>1633.674</v>
+        <v>1673.463</v>
       </c>
       <c r="F68">
-        <v>2626.074</v>
+        <v>2665.863</v>
       </c>
       <c r="G68">
         <v>126.5</v>
@@ -7003,28 +7003,28 @@
         <v>382.3</v>
       </c>
       <c r="M68">
-        <v>236.34666</v>
+        <v>239.92767</v>
       </c>
       <c r="N68">
-        <v>145.95334</v>
+        <v>142.3723299999999</v>
       </c>
       <c r="O68">
-        <v>39.4074018</v>
+        <v>38.44052909999999</v>
       </c>
       <c r="P68">
-        <v>106.5459382</v>
+        <v>103.9318009</v>
       </c>
       <c r="Q68">
-        <v>164.7459382</v>
+        <v>162.1318008999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2396090615130348</v>
+        <v>0.2448260137650948</v>
       </c>
       <c r="T68">
-        <v>2.321782617086044</v>
+        <v>2.384280360785124</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.617539253569312</v>
+        <v>1.593396876650367</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7049,22 +7049,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1248115845424813</v>
+        <v>0.1247940881705307</v>
       </c>
       <c r="C69">
-        <v>1274.341162388733</v>
+        <v>1235.396858341048</v>
       </c>
       <c r="D69">
-        <v>3813.704162388733</v>
+        <v>3814.548858341048</v>
       </c>
       <c r="E69">
-        <v>1673.463</v>
+        <v>1713.252</v>
       </c>
       <c r="F69">
-        <v>2665.863</v>
+        <v>2705.652</v>
       </c>
       <c r="G69">
         <v>126.5</v>
@@ -7085,28 +7085,28 @@
         <v>382.3</v>
       </c>
       <c r="M69">
-        <v>239.92767</v>
+        <v>243.50868</v>
       </c>
       <c r="N69">
-        <v>142.3723299999999</v>
+        <v>138.79132</v>
       </c>
       <c r="O69">
-        <v>38.44052909999999</v>
+        <v>37.47365639999999</v>
       </c>
       <c r="P69">
-        <v>103.9318009</v>
+        <v>101.3176636</v>
       </c>
       <c r="Q69">
-        <v>162.1318008999999</v>
+        <v>159.5176636</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2448260137650948</v>
+        <v>0.2503690255329085</v>
       </c>
       <c r="T69">
-        <v>2.384280360785124</v>
+        <v>2.450684213465395</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.593396876650367</v>
+        <v>1.569964569640803</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7131,22 +7131,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1247940881705307</v>
+        <v>0.1247765917985801</v>
       </c>
       <c r="C70">
-        <v>1235.396858341048</v>
+        <v>1196.452928559062</v>
       </c>
       <c r="D70">
-        <v>3814.548858341048</v>
+        <v>3815.393928559062</v>
       </c>
       <c r="E70">
-        <v>1713.252</v>
+        <v>1753.041</v>
       </c>
       <c r="F70">
-        <v>2705.652</v>
+        <v>2745.441</v>
       </c>
       <c r="G70">
         <v>126.5</v>
@@ -7167,28 +7167,28 @@
         <v>382.3</v>
       </c>
       <c r="M70">
-        <v>243.50868</v>
+        <v>247.08969</v>
       </c>
       <c r="N70">
-        <v>138.79132</v>
+        <v>135.2103099999999</v>
       </c>
       <c r="O70">
-        <v>37.47365639999999</v>
+        <v>36.50678369999999</v>
       </c>
       <c r="P70">
-        <v>101.3176636</v>
+        <v>98.70352629999995</v>
       </c>
       <c r="Q70">
-        <v>159.5176636</v>
+        <v>156.9035263</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2503690255329085</v>
+        <v>0.2562696509631618</v>
       </c>
       <c r="T70">
-        <v>2.450684213465395</v>
+        <v>2.521372185673426</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.569964569640803</v>
+        <v>1.547211459935864</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7213,22 +7213,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1247765917985801</v>
+        <v>0.1247590954266296</v>
       </c>
       <c r="C71">
-        <v>1196.452928559062</v>
+        <v>1157.509373291567</v>
       </c>
       <c r="D71">
-        <v>3815.393928559062</v>
+        <v>3816.239373291568</v>
       </c>
       <c r="E71">
-        <v>1753.041</v>
+        <v>1792.83</v>
       </c>
       <c r="F71">
-        <v>2745.441</v>
+        <v>2785.23</v>
       </c>
       <c r="G71">
         <v>126.5</v>
@@ -7249,28 +7249,28 @@
         <v>382.3</v>
       </c>
       <c r="M71">
-        <v>247.08969</v>
+        <v>250.6707</v>
       </c>
       <c r="N71">
-        <v>135.2103099999999</v>
+        <v>131.6292999999999</v>
       </c>
       <c r="O71">
-        <v>36.50678369999999</v>
+        <v>35.53991099999998</v>
       </c>
       <c r="P71">
-        <v>98.70352629999995</v>
+        <v>96.08938899999993</v>
       </c>
       <c r="Q71">
-        <v>156.9035263</v>
+        <v>154.2893889999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2562696509631618</v>
+        <v>0.2625636514220988</v>
       </c>
       <c r="T71">
-        <v>2.521372185673426</v>
+        <v>2.596772689361994</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.547211459935864</v>
+        <v>1.525108439079637</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7295,22 +7295,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1247590954266296</v>
+        <v>0.124741599054679</v>
       </c>
       <c r="C72">
-        <v>1157.509373291567</v>
+        <v>1118.566192787588</v>
       </c>
       <c r="D72">
-        <v>3816.239373291568</v>
+        <v>3817.085192787588</v>
       </c>
       <c r="E72">
-        <v>1792.83</v>
+        <v>1832.619</v>
       </c>
       <c r="F72">
-        <v>2785.23</v>
+        <v>2825.019</v>
       </c>
       <c r="G72">
         <v>126.5</v>
@@ -7331,28 +7331,28 @@
         <v>382.3</v>
       </c>
       <c r="M72">
-        <v>250.6707</v>
+        <v>254.25171</v>
       </c>
       <c r="N72">
-        <v>131.6292999999999</v>
+        <v>128.04829</v>
       </c>
       <c r="O72">
-        <v>35.53991099999998</v>
+        <v>34.57303829999999</v>
       </c>
       <c r="P72">
-        <v>96.08938899999993</v>
+        <v>93.47525169999997</v>
       </c>
       <c r="Q72">
-        <v>154.2893889999999</v>
+        <v>151.6752517</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2625636514220988</v>
+        <v>0.2692917208782037</v>
       </c>
       <c r="T72">
-        <v>2.596772689361994</v>
+        <v>2.677373227787703</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.525108439079637</v>
+        <v>1.50362803852922</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7377,22 +7377,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1247415990546791</v>
+        <v>0.1585918777283267</v>
       </c>
       <c r="C73">
-        <v>1118.566192787588</v>
+        <v>-66.77867612108275</v>
       </c>
       <c r="D73">
-        <v>3817.085192787588</v>
+        <v>2671.529323878917</v>
       </c>
       <c r="E73">
-        <v>1832.619</v>
+        <v>1872.408</v>
       </c>
       <c r="F73">
-        <v>2825.019</v>
+        <v>2864.808</v>
       </c>
       <c r="G73">
         <v>126.5</v>
@@ -7413,45 +7413,45 @@
         <v>382.3</v>
       </c>
       <c r="M73">
-        <v>254.25171</v>
+        <v>420.5538144</v>
       </c>
       <c r="N73">
-        <v>128.04829</v>
+        <v>-38.25381440000007</v>
       </c>
       <c r="O73">
-        <v>34.5730383</v>
+        <v>-10.32852988800002</v>
       </c>
       <c r="P73">
-        <v>93.47525169999997</v>
+        <v>-27.92528451200005</v>
       </c>
       <c r="Q73">
-        <v>151.6752517</v>
+        <v>30.27471548799994</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2692917208782036</v>
+        <v>0.2815641867038259</v>
       </c>
       <c r="T73">
-        <v>2.677373227787702</v>
+        <v>2.824394206065315</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.27</v>
+        <v>0.2454406462755887</v>
       </c>
       <c r="W73">
-        <v>0.06569999999999999</v>
+        <v>0.1107693131267436</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.50362803852922</v>
+        <v>0.9090394306503286</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7459,22 +7459,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1585918777283267</v>
+        <v>0.1596018777283267</v>
       </c>
       <c r="C74">
-        <v>-66.77867612108275</v>
+        <v>-130.2776945406299</v>
       </c>
       <c r="D74">
-        <v>2671.529323878917</v>
+        <v>2647.81930545937</v>
       </c>
       <c r="E74">
-        <v>1872.408</v>
+        <v>1912.197</v>
       </c>
       <c r="F74">
-        <v>2864.808</v>
+        <v>2904.597</v>
       </c>
       <c r="G74">
         <v>126.5</v>
@@ -7495,37 +7495,37 @@
         <v>382.3</v>
       </c>
       <c r="M74">
-        <v>420.5538144</v>
+        <v>426.3948396000001</v>
       </c>
       <c r="N74">
-        <v>-38.25381440000007</v>
+        <v>-44.09483960000011</v>
       </c>
       <c r="O74">
-        <v>-10.32852988800002</v>
+        <v>-11.90560669200003</v>
       </c>
       <c r="P74">
-        <v>-27.92528451200005</v>
+        <v>-32.18923290800008</v>
       </c>
       <c r="Q74">
-        <v>30.27471548799994</v>
+        <v>26.01076709199991</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2815641867038259</v>
+        <v>0.2902961936187824</v>
       </c>
       <c r="T74">
-        <v>2.824394206065315</v>
+        <v>2.929001398882549</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2454406462755887</v>
+        <v>0.2420784456416765</v>
       </c>
       <c r="W74">
-        <v>0.1107693131267436</v>
+        <v>0.1112628841798019</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9090394306503286</v>
+        <v>0.8965868357099129</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7541,22 +7541,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1596018777283267</v>
+        <v>0.1606118777283266</v>
       </c>
       <c r="C75">
-        <v>-130.2776945406299</v>
+        <v>-193.3595589326046</v>
       </c>
       <c r="D75">
-        <v>2647.81930545937</v>
+        <v>2624.526441067395</v>
       </c>
       <c r="E75">
-        <v>1912.197</v>
+        <v>1951.986</v>
       </c>
       <c r="F75">
-        <v>2904.597</v>
+        <v>2944.386</v>
       </c>
       <c r="G75">
         <v>126.5</v>
@@ -7577,37 +7577,37 @@
         <v>382.3</v>
       </c>
       <c r="M75">
-        <v>426.3948396000001</v>
+        <v>432.2358648000001</v>
       </c>
       <c r="N75">
-        <v>-44.09483960000011</v>
+        <v>-49.9358648000001</v>
       </c>
       <c r="O75">
-        <v>-11.90560669200003</v>
+        <v>-13.48268349600003</v>
       </c>
       <c r="P75">
-        <v>-32.18923290800008</v>
+        <v>-36.45318130400008</v>
       </c>
       <c r="Q75">
-        <v>26.01076709199991</v>
+        <v>21.74681869599991</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2902961936187824</v>
+        <v>0.299699893373351</v>
       </c>
       <c r="T75">
-        <v>2.929001398882549</v>
+        <v>3.04165529883957</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2420784456416765</v>
+        <v>0.2388071152951674</v>
       </c>
       <c r="W75">
-        <v>0.1112628841798019</v>
+        <v>0.1117431154746694</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8965868357099129</v>
+        <v>0.8844707973895087</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7623,22 +7623,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1606118777283266</v>
+        <v>0.1616218777283266</v>
       </c>
       <c r="C76">
-        <v>-193.3595589326046</v>
+        <v>-256.0351824053805</v>
       </c>
       <c r="D76">
-        <v>2624.526441067395</v>
+        <v>2601.63981759462</v>
       </c>
       <c r="E76">
-        <v>1951.986</v>
+        <v>1991.775</v>
       </c>
       <c r="F76">
-        <v>2944.386</v>
+        <v>2984.175</v>
       </c>
       <c r="G76">
         <v>126.5</v>
@@ -7659,37 +7659,37 @@
         <v>382.3</v>
       </c>
       <c r="M76">
-        <v>432.2358648000001</v>
+        <v>438.07689</v>
       </c>
       <c r="N76">
-        <v>-49.9358648000001</v>
+        <v>-55.77689000000009</v>
       </c>
       <c r="O76">
-        <v>-13.48268349600003</v>
+        <v>-15.05976030000003</v>
       </c>
       <c r="P76">
-        <v>-36.45318130400008</v>
+        <v>-40.71712970000007</v>
       </c>
       <c r="Q76">
-        <v>21.74681869599991</v>
+        <v>17.48287029999992</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.299699893373351</v>
+        <v>0.309855889108285</v>
       </c>
       <c r="T76">
-        <v>3.04165529883957</v>
+        <v>3.163321510793153</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2388071152951674</v>
+        <v>0.2356230204245652</v>
       </c>
       <c r="W76">
-        <v>0.1117431154746694</v>
+        <v>0.1122105406016738</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8844707973895087</v>
+        <v>0.8726778534243154</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7705,22 +7705,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1616218777283266</v>
+        <v>0.1626318777283267</v>
       </c>
       <c r="C77">
-        <v>-256.0351824053805</v>
+        <v>-318.315100696369</v>
       </c>
       <c r="D77">
-        <v>2601.63981759462</v>
+        <v>2579.148899303631</v>
       </c>
       <c r="E77">
-        <v>1991.775</v>
+        <v>2031.564</v>
       </c>
       <c r="F77">
-        <v>2984.175</v>
+        <v>3023.964</v>
       </c>
       <c r="G77">
         <v>126.5</v>
@@ -7741,37 +7741,37 @@
         <v>382.3</v>
       </c>
       <c r="M77">
-        <v>438.07689</v>
+        <v>443.9179152</v>
       </c>
       <c r="N77">
-        <v>-55.77689000000009</v>
+        <v>-61.61791520000008</v>
       </c>
       <c r="O77">
-        <v>-15.05976030000003</v>
+        <v>-16.63683710400002</v>
       </c>
       <c r="P77">
-        <v>-40.71712970000007</v>
+        <v>-44.98107809600006</v>
       </c>
       <c r="Q77">
-        <v>17.48287029999992</v>
+        <v>13.21892190399993</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.309855889108285</v>
+        <v>0.3208582178211303</v>
       </c>
       <c r="T77">
-        <v>3.163321510793153</v>
+        <v>3.295126573742868</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2356230204245652</v>
+        <v>0.2325227175242419</v>
       </c>
       <c r="W77">
-        <v>0.1122105406016738</v>
+        <v>0.1126656650674413</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8726778534243154</v>
+        <v>0.8611952500897849</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7787,22 +7787,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1626318777283267</v>
+        <v>0.1636418777283267</v>
       </c>
       <c r="C78">
-        <v>-318.315100696369</v>
+        <v>-380.2094883438931</v>
       </c>
       <c r="D78">
-        <v>2579.148899303631</v>
+        <v>2557.043511656107</v>
       </c>
       <c r="E78">
-        <v>2031.564</v>
+        <v>2071.353</v>
       </c>
       <c r="F78">
-        <v>3023.964</v>
+        <v>3063.753</v>
       </c>
       <c r="G78">
         <v>126.5</v>
@@ -7823,37 +7823,37 @@
         <v>382.3</v>
       </c>
       <c r="M78">
-        <v>443.9179152</v>
+        <v>449.7589404000001</v>
       </c>
       <c r="N78">
-        <v>-61.61791520000008</v>
+        <v>-67.45894040000013</v>
       </c>
       <c r="O78">
-        <v>-16.63683710400002</v>
+        <v>-18.21391390800004</v>
       </c>
       <c r="P78">
-        <v>-44.98107809600006</v>
+        <v>-49.24502649200009</v>
       </c>
       <c r="Q78">
-        <v>13.21892190399993</v>
+        <v>8.954973507999895</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3208582178211303</v>
+        <v>0.3328172707698751</v>
       </c>
       <c r="T78">
-        <v>3.295126573742868</v>
+        <v>3.438392946514297</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2325227175242419</v>
+        <v>0.229502941971979</v>
       </c>
       <c r="W78">
-        <v>0.1126656650674413</v>
+        <v>0.1131089681185135</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8611952500897849</v>
+        <v>0.8500108961925149</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7869,22 +7869,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1636418777283267</v>
+        <v>0.1646518777283267</v>
       </c>
       <c r="C79">
-        <v>-380.2094883438931</v>
+        <v>-441.7281740344802</v>
       </c>
       <c r="D79">
-        <v>2557.043511656107</v>
+        <v>2535.31382596552</v>
       </c>
       <c r="E79">
-        <v>2071.353</v>
+        <v>2111.142</v>
       </c>
       <c r="F79">
-        <v>3063.753</v>
+        <v>3103.542</v>
       </c>
       <c r="G79">
         <v>126.5</v>
@@ -7905,37 +7905,37 @@
         <v>382.3</v>
       </c>
       <c r="M79">
-        <v>449.7589404000001</v>
+        <v>455.5999656000001</v>
       </c>
       <c r="N79">
-        <v>-67.45894040000013</v>
+        <v>-73.29996560000012</v>
       </c>
       <c r="O79">
-        <v>-18.21391390800004</v>
+        <v>-19.79099071200003</v>
       </c>
       <c r="P79">
-        <v>-49.24502649200009</v>
+        <v>-53.50897488800008</v>
       </c>
       <c r="Q79">
-        <v>8.954973507999895</v>
+        <v>4.691025111999906</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3328172707698751</v>
+        <v>0.345863510350324</v>
       </c>
       <c r="T79">
-        <v>3.438392946514297</v>
+        <v>3.59468353499222</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.229502941971979</v>
+        <v>0.2265605965620819</v>
       </c>
       <c r="W79">
-        <v>0.1131089681185135</v>
+        <v>0.1135409044246864</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8500108961925149</v>
+        <v>0.8391133206003032</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7951,22 +7951,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1646518777283267</v>
+        <v>0.1656618777283267</v>
       </c>
       <c r="C80">
-        <v>-441.7281740344802</v>
+        <v>-502.8806551742396</v>
       </c>
       <c r="D80">
-        <v>2535.31382596552</v>
+        <v>2513.950344825761</v>
       </c>
       <c r="E80">
-        <v>2111.142</v>
+        <v>2150.931</v>
       </c>
       <c r="F80">
-        <v>3103.542</v>
+        <v>3143.331</v>
       </c>
       <c r="G80">
         <v>126.5</v>
@@ -7987,37 +7987,37 @@
         <v>382.3</v>
       </c>
       <c r="M80">
-        <v>455.5999656000001</v>
+        <v>461.4409908000001</v>
       </c>
       <c r="N80">
-        <v>-73.29996560000012</v>
+        <v>-79.14099080000011</v>
       </c>
       <c r="O80">
-        <v>-19.79099071200003</v>
+        <v>-21.36806751600003</v>
       </c>
       <c r="P80">
-        <v>-53.50897488800008</v>
+        <v>-57.77292328400008</v>
       </c>
       <c r="Q80">
-        <v>4.691025111999906</v>
+        <v>0.4270767159999096</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.345863510350324</v>
+        <v>0.3601522489384347</v>
       </c>
       <c r="T80">
-        <v>3.59468353499222</v>
+        <v>3.765858941420421</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2265605965620819</v>
+        <v>0.2236927409093973</v>
       </c>
       <c r="W80">
-        <v>0.1135409044246864</v>
+        <v>0.1139619056345005</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8391133206003032</v>
+        <v>0.8284916329977677</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8033,22 +8033,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1656618777283267</v>
+        <v>0.1666718777283267</v>
       </c>
       <c r="C81">
-        <v>-502.8806551742396</v>
+        <v>-563.6761117296751</v>
       </c>
       <c r="D81">
-        <v>2513.950344825761</v>
+        <v>2492.943888270325</v>
       </c>
       <c r="E81">
-        <v>2150.931</v>
+        <v>2190.72</v>
       </c>
       <c r="F81">
-        <v>3143.331</v>
+        <v>3183.12</v>
       </c>
       <c r="G81">
         <v>126.5</v>
@@ -8069,37 +8069,37 @@
         <v>382.3</v>
       </c>
       <c r="M81">
-        <v>461.4409908000001</v>
+        <v>467.2820160000001</v>
       </c>
       <c r="N81">
-        <v>-79.14099080000011</v>
+        <v>-84.98201600000016</v>
       </c>
       <c r="O81">
-        <v>-21.36806751600003</v>
+        <v>-22.94514432000004</v>
       </c>
       <c r="P81">
-        <v>-57.77292328400008</v>
+        <v>-62.03687168000012</v>
       </c>
       <c r="Q81">
-        <v>0.4270767159999096</v>
+        <v>-3.836871680000129</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3601522489384347</v>
+        <v>0.3758698613853564</v>
       </c>
       <c r="T81">
-        <v>3.765858941420421</v>
+        <v>3.954151888491443</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2236927409093973</v>
+        <v>0.2208965816480298</v>
       </c>
       <c r="W81">
-        <v>0.1139619056345005</v>
+        <v>0.1143723818140692</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8284916329977677</v>
+        <v>0.8181354875852955</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8115,22 +8115,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1666718777283267</v>
+        <v>0.1676818777283267</v>
       </c>
       <c r="C82">
-        <v>-563.6761117296751</v>
+        <v>-624.1234193803434</v>
       </c>
       <c r="D82">
-        <v>2492.943888270325</v>
+        <v>2472.285580619657</v>
       </c>
       <c r="E82">
-        <v>2190.72</v>
+        <v>2230.509</v>
       </c>
       <c r="F82">
-        <v>3183.12</v>
+        <v>3222.909</v>
       </c>
       <c r="G82">
         <v>126.5</v>
@@ -8151,37 +8151,37 @@
         <v>382.3</v>
       </c>
       <c r="M82">
-        <v>467.2820160000001</v>
+        <v>473.1230412</v>
       </c>
       <c r="N82">
-        <v>-84.98201600000016</v>
+        <v>-90.82304120000009</v>
       </c>
       <c r="O82">
-        <v>-22.94514432000004</v>
+        <v>-24.52222112400003</v>
       </c>
       <c r="P82">
-        <v>-62.03687168000012</v>
+        <v>-66.30082007600006</v>
       </c>
       <c r="Q82">
-        <v>-3.836871680000129</v>
+        <v>-8.100820076000076</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3758698613853564</v>
+        <v>0.3932419593530068</v>
       </c>
       <c r="T82">
-        <v>3.954151888491443</v>
+        <v>4.162265145780466</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2208965816480298</v>
+        <v>0.2181694633560789</v>
       </c>
       <c r="W82">
-        <v>0.1143723818140692</v>
+        <v>0.1147727227793276</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8181354875852955</v>
+        <v>0.8080350494669586</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8197,22 +8197,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1676818777283267</v>
+        <v>0.216782499919807</v>
       </c>
       <c r="C83">
-        <v>-624.1234193803434</v>
+        <v>-1373.872563256964</v>
       </c>
       <c r="D83">
-        <v>2472.285580619657</v>
+        <v>1762.325436743037</v>
       </c>
       <c r="E83">
-        <v>2230.509</v>
+        <v>2270.298</v>
       </c>
       <c r="F83">
-        <v>3222.909</v>
+        <v>3262.698</v>
       </c>
       <c r="G83">
         <v>126.5</v>
@@ -8233,45 +8233,45 @@
         <v>382.3</v>
       </c>
       <c r="M83">
-        <v>473.1230412</v>
+        <v>655.1497584000001</v>
       </c>
       <c r="N83">
-        <v>-90.82304120000009</v>
+        <v>-272.8497584000002</v>
       </c>
       <c r="O83">
-        <v>-24.52222112400003</v>
+        <v>-73.66943476800004</v>
       </c>
       <c r="P83">
-        <v>-66.30082007600006</v>
+        <v>-199.1803236320001</v>
       </c>
       <c r="Q83">
-        <v>-8.100820076000076</v>
+        <v>-140.9803236320001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3932419593530068</v>
+        <v>0.4337144137141756</v>
       </c>
       <c r="T83">
-        <v>4.162265145780466</v>
+        <v>4.647114720268757</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.2181694633560789</v>
+        <v>0.1575532901852627</v>
       </c>
       <c r="W83">
-        <v>0.1147727227793276</v>
+        <v>0.1691632993307992</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8080350494669586</v>
+        <v>0.583530704389862</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8279,22 +8279,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.216782499919807</v>
+        <v>0.218332499919807</v>
       </c>
       <c r="C84">
-        <v>-1373.872563256964</v>
+        <v>-1429.493968329755</v>
       </c>
       <c r="D84">
-        <v>1762.325436743037</v>
+        <v>1746.493031670246</v>
       </c>
       <c r="E84">
-        <v>2270.298</v>
+        <v>2310.087</v>
       </c>
       <c r="F84">
-        <v>3262.698</v>
+        <v>3302.487000000001</v>
       </c>
       <c r="G84">
         <v>126.5</v>
@@ -8315,37 +8315,37 @@
         <v>382.3</v>
       </c>
       <c r="M84">
-        <v>655.1497584000001</v>
+        <v>663.1393896000001</v>
       </c>
       <c r="N84">
-        <v>-272.8497584000002</v>
+        <v>-280.8393896000001</v>
       </c>
       <c r="O84">
-        <v>-73.66943476800004</v>
+        <v>-75.82663519200004</v>
       </c>
       <c r="P84">
-        <v>-199.1803236320001</v>
+        <v>-205.0127544080001</v>
       </c>
       <c r="Q84">
-        <v>-140.9803236320001</v>
+        <v>-146.8127544080001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4337144137141756</v>
+        <v>0.4565329086385388</v>
       </c>
       <c r="T84">
-        <v>4.647114720268757</v>
+        <v>4.920474409696331</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1575532901852627</v>
+        <v>0.1556550577733921</v>
       </c>
       <c r="W84">
-        <v>0.1691632993307992</v>
+        <v>0.1695444643991029</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.583530704389862</v>
+        <v>0.5765002139755263</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8361,22 +8361,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.218332499919807</v>
+        <v>0.219882499919807</v>
       </c>
       <c r="C85">
-        <v>-1429.493968329755</v>
+        <v>-1484.833435495242</v>
       </c>
       <c r="D85">
-        <v>1746.493031670246</v>
+        <v>1730.942564504758</v>
       </c>
       <c r="E85">
-        <v>2310.087</v>
+        <v>2349.876</v>
       </c>
       <c r="F85">
-        <v>3302.487000000001</v>
+        <v>3342.276</v>
       </c>
       <c r="G85">
         <v>126.5</v>
@@ -8397,37 +8397,37 @@
         <v>382.3</v>
       </c>
       <c r="M85">
-        <v>663.1393896000001</v>
+        <v>671.1290208</v>
       </c>
       <c r="N85">
-        <v>-280.8393896000001</v>
+        <v>-288.8290208000001</v>
       </c>
       <c r="O85">
-        <v>-75.82663519200004</v>
+        <v>-77.98383561600002</v>
       </c>
       <c r="P85">
-        <v>-205.0127544080001</v>
+        <v>-210.8451851840001</v>
       </c>
       <c r="Q85">
-        <v>-146.8127544080001</v>
+        <v>-152.6451851840001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4565329086385388</v>
+        <v>0.4822037154284476</v>
       </c>
       <c r="T85">
-        <v>4.920474409696331</v>
+        <v>5.228004060302353</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1556550577733921</v>
+        <v>0.1538020213713279</v>
       </c>
       <c r="W85">
-        <v>0.1695444643991029</v>
+        <v>0.1699165541086373</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5765002139755263</v>
+        <v>0.5696371161901035</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8443,22 +8443,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.219882499919807</v>
+        <v>0.221432499919807</v>
       </c>
       <c r="C86">
-        <v>-1484.833435495242</v>
+        <v>-1539.898429267507</v>
       </c>
       <c r="D86">
-        <v>1730.942564504758</v>
+        <v>1715.666570732493</v>
       </c>
       <c r="E86">
-        <v>2349.876</v>
+        <v>2389.665</v>
       </c>
       <c r="F86">
-        <v>3342.276</v>
+        <v>3382.065</v>
       </c>
       <c r="G86">
         <v>126.5</v>
@@ -8479,37 +8479,37 @@
         <v>382.3</v>
       </c>
       <c r="M86">
-        <v>671.1290208</v>
+        <v>679.118652</v>
       </c>
       <c r="N86">
-        <v>-288.8290208000001</v>
+        <v>-296.818652</v>
       </c>
       <c r="O86">
-        <v>-77.98383561600002</v>
+        <v>-80.14103604000002</v>
       </c>
       <c r="P86">
-        <v>-210.8451851840001</v>
+        <v>-216.67761596</v>
       </c>
       <c r="Q86">
-        <v>-152.6451851840001</v>
+        <v>-158.47761596</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4822037154284473</v>
+        <v>0.5112972964570105</v>
       </c>
       <c r="T86">
-        <v>5.228004060302349</v>
+        <v>5.576537664322506</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1538020213713279</v>
+        <v>0.1519925858257829</v>
       </c>
       <c r="W86">
-        <v>0.1699165541086373</v>
+        <v>0.1702798887661828</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5696371161901035</v>
+        <v>0.5629355030584552</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8525,22 +8525,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.221432499919807</v>
+        <v>0.222982499919807</v>
       </c>
       <c r="C87">
-        <v>-1539.898429267507</v>
+        <v>-1594.696152961094</v>
       </c>
       <c r="D87">
-        <v>1715.666570732493</v>
+        <v>1700.657847038906</v>
       </c>
       <c r="E87">
-        <v>2389.665</v>
+        <v>2429.454</v>
       </c>
       <c r="F87">
-        <v>3382.065</v>
+        <v>3421.854</v>
       </c>
       <c r="G87">
         <v>126.5</v>
@@ -8561,37 +8561,37 @@
         <v>382.3</v>
       </c>
       <c r="M87">
-        <v>679.118652</v>
+        <v>687.1082832</v>
       </c>
       <c r="N87">
-        <v>-296.818652</v>
+        <v>-304.8082832</v>
       </c>
       <c r="O87">
-        <v>-80.14103604000002</v>
+        <v>-82.29823646400001</v>
       </c>
       <c r="P87">
-        <v>-216.67761596</v>
+        <v>-222.510046736</v>
       </c>
       <c r="Q87">
-        <v>-158.47761596</v>
+        <v>-164.310046736</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5112972964570105</v>
+        <v>0.544547103346797</v>
       </c>
       <c r="T87">
-        <v>5.576537664322506</v>
+        <v>5.974861783202686</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1519925858257829</v>
+        <v>0.1502252301766459</v>
       </c>
       <c r="W87">
-        <v>0.1702798887661828</v>
+        <v>0.1706347737805295</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5629355030584552</v>
+        <v>0.5563897413949848</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8607,22 +8607,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.222982499919807</v>
+        <v>0.2245324999198069</v>
       </c>
       <c r="C88">
-        <v>-1594.696152961094</v>
+        <v>-1649.233560016851</v>
       </c>
       <c r="D88">
-        <v>1700.657847038906</v>
+        <v>1685.909439983149</v>
       </c>
       <c r="E88">
-        <v>2429.454</v>
+        <v>2469.243</v>
       </c>
       <c r="F88">
-        <v>3421.854</v>
+        <v>3461.643</v>
       </c>
       <c r="G88">
         <v>126.5</v>
@@ -8643,37 +8643,37 @@
         <v>382.3</v>
       </c>
       <c r="M88">
-        <v>687.1082832</v>
+        <v>695.0979144</v>
       </c>
       <c r="N88">
-        <v>-304.8082832</v>
+        <v>-312.7979144000001</v>
       </c>
       <c r="O88">
-        <v>-82.29823646400001</v>
+        <v>-84.45543688800002</v>
       </c>
       <c r="P88">
-        <v>-222.510046736</v>
+        <v>-228.3424775120001</v>
       </c>
       <c r="Q88">
-        <v>-164.310046736</v>
+        <v>-170.1424775120001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.544547103346797</v>
+        <v>0.5829122651427044</v>
       </c>
       <c r="T88">
-        <v>5.974861783202686</v>
+        <v>6.434466535756738</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1502252301766459</v>
+        <v>0.1484985033930063</v>
       </c>
       <c r="W88">
-        <v>0.1706347737805295</v>
+        <v>0.1709815005186844</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5563897413949848</v>
+        <v>0.5499944570111344</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8689,22 +8689,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2245324999198069</v>
+        <v>0.226082499919807</v>
       </c>
       <c r="C89">
-        <v>-1649.233560016851</v>
+        <v>-1703.517364743523</v>
       </c>
       <c r="D89">
-        <v>1685.909439983149</v>
+        <v>1671.414635256477</v>
       </c>
       <c r="E89">
-        <v>2469.243</v>
+        <v>2509.032</v>
       </c>
       <c r="F89">
-        <v>3461.643</v>
+        <v>3501.432</v>
       </c>
       <c r="G89">
         <v>126.5</v>
@@ -8725,37 +8725,37 @@
         <v>382.3</v>
       </c>
       <c r="M89">
-        <v>695.0979144</v>
+        <v>703.0875456000001</v>
       </c>
       <c r="N89">
-        <v>-312.7979144000001</v>
+        <v>-320.7875456000002</v>
       </c>
       <c r="O89">
-        <v>-84.45543688800002</v>
+        <v>-86.61263731200005</v>
       </c>
       <c r="P89">
-        <v>-228.3424775120001</v>
+        <v>-234.1749082880001</v>
       </c>
       <c r="Q89">
-        <v>-170.1424775120001</v>
+        <v>-175.9749082880001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5829122651427044</v>
+        <v>0.6276716205712631</v>
       </c>
       <c r="T89">
-        <v>6.434466535756738</v>
+        <v>6.970672080403133</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1484985033930063</v>
+        <v>0.1468110203999039</v>
       </c>
       <c r="W89">
-        <v>0.1709815005186844</v>
+        <v>0.1713203471036993</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5499944570111344</v>
+        <v>0.5437445199996441</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8771,22 +8771,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.226082499919807</v>
+        <v>0.2276324999198069</v>
       </c>
       <c r="C90">
-        <v>-1703.517364743523</v>
+        <v>-1757.554052509956</v>
       </c>
       <c r="D90">
-        <v>1671.414635256477</v>
+        <v>1657.166947490044</v>
       </c>
       <c r="E90">
-        <v>2509.032</v>
+        <v>2548.821</v>
       </c>
       <c r="F90">
-        <v>3501.432</v>
+        <v>3541.221</v>
       </c>
       <c r="G90">
         <v>126.5</v>
@@ -8807,37 +8807,37 @@
         <v>382.3</v>
       </c>
       <c r="M90">
-        <v>703.0875456000001</v>
+        <v>711.0771768000001</v>
       </c>
       <c r="N90">
-        <v>-320.7875456000002</v>
+        <v>-328.7771768000001</v>
       </c>
       <c r="O90">
-        <v>-86.61263731200005</v>
+        <v>-88.76983773600004</v>
       </c>
       <c r="P90">
-        <v>-234.1749082880001</v>
+        <v>-240.0073390640001</v>
       </c>
       <c r="Q90">
-        <v>-175.9749082880001</v>
+        <v>-181.8073390640001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6276716205712631</v>
+        <v>0.6805690406231962</v>
       </c>
       <c r="T90">
-        <v>6.970672080403133</v>
+        <v>7.604369542257965</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1468110203999039</v>
+        <v>0.1451614583729387</v>
       </c>
       <c r="W90">
-        <v>0.1713203471036993</v>
+        <v>0.1716515791587139</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5437445199996441</v>
+        <v>0.5376350310108842</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8853,22 +8853,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2276324999198069</v>
+        <v>0.2291824999198069</v>
       </c>
       <c r="C91">
-        <v>-1757.554052509956</v>
+        <v>-1811.349889420419</v>
       </c>
       <c r="D91">
-        <v>1657.166947490044</v>
+        <v>1643.160110579581</v>
       </c>
       <c r="E91">
-        <v>2548.821</v>
+        <v>2588.61</v>
       </c>
       <c r="F91">
-        <v>3541.221</v>
+        <v>3581.01</v>
       </c>
       <c r="G91">
         <v>126.5</v>
@@ -8889,37 +8889,37 @@
         <v>382.3</v>
       </c>
       <c r="M91">
-        <v>711.0771768000001</v>
+        <v>719.066808</v>
       </c>
       <c r="N91">
-        <v>-328.7771768000001</v>
+        <v>-336.7668080000001</v>
       </c>
       <c r="O91">
-        <v>-88.76983773600004</v>
+        <v>-90.92703816000002</v>
       </c>
       <c r="P91">
-        <v>-240.0073390640001</v>
+        <v>-245.8397698400001</v>
       </c>
       <c r="Q91">
-        <v>-181.8073390640001</v>
+        <v>-187.6397698400001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6805690406231962</v>
+        <v>0.7440459446855158</v>
       </c>
       <c r="T91">
-        <v>7.604369542257965</v>
+        <v>8.364806496483761</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1451614583729387</v>
+        <v>0.1435485532799061</v>
       </c>
       <c r="W91">
-        <v>0.1716515791587139</v>
+        <v>0.1719754505013948</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5376350310108842</v>
+        <v>0.5316613084440965</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8935,22 +8935,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2291824999198069</v>
+        <v>0.230732499919807</v>
       </c>
       <c r="C92">
-        <v>-1811.349889420419</v>
+        <v>-1864.910931503357</v>
       </c>
       <c r="D92">
-        <v>1643.160110579581</v>
+        <v>1629.388068496644</v>
       </c>
       <c r="E92">
-        <v>2588.61</v>
+        <v>2628.399</v>
       </c>
       <c r="F92">
-        <v>3581.01</v>
+        <v>3620.799</v>
       </c>
       <c r="G92">
         <v>126.5</v>
@@ -8971,37 +8971,37 @@
         <v>382.3</v>
       </c>
       <c r="M92">
-        <v>719.066808</v>
+        <v>727.0564392000001</v>
       </c>
       <c r="N92">
-        <v>-336.7668080000001</v>
+        <v>-344.7564392000002</v>
       </c>
       <c r="O92">
-        <v>-90.92703816000002</v>
+        <v>-93.08423858400005</v>
       </c>
       <c r="P92">
-        <v>-245.8397698400001</v>
+        <v>-251.6722006160001</v>
       </c>
       <c r="Q92">
-        <v>-187.6397698400001</v>
+        <v>-193.4722006160001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7440459446855158</v>
+        <v>0.8216288274283511</v>
       </c>
       <c r="T92">
-        <v>8.364806496483761</v>
+        <v>9.294229440537514</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1435485532799061</v>
+        <v>0.1419710966504565</v>
       </c>
       <c r="W92">
-        <v>0.1719754505013948</v>
+        <v>0.1722922037925883</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5316613084440965</v>
+        <v>0.5258188764831724</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9017,22 +9017,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.230732499919807</v>
+        <v>0.232282499919807</v>
       </c>
       <c r="C93">
-        <v>-1864.910931503357</v>
+        <v>-1918.243033441908</v>
       </c>
       <c r="D93">
-        <v>1629.388068496644</v>
+        <v>1615.844966558093</v>
       </c>
       <c r="E93">
-        <v>2628.399</v>
+        <v>2668.188</v>
       </c>
       <c r="F93">
-        <v>3620.799</v>
+        <v>3660.588</v>
       </c>
       <c r="G93">
         <v>126.5</v>
@@ -9053,37 +9053,37 @@
         <v>382.3</v>
       </c>
       <c r="M93">
-        <v>727.0564392000001</v>
+        <v>735.0460704000001</v>
       </c>
       <c r="N93">
-        <v>-344.7564392000002</v>
+        <v>-352.7460704000001</v>
       </c>
       <c r="O93">
-        <v>-93.08423858400005</v>
+        <v>-95.24143900800004</v>
       </c>
       <c r="P93">
-        <v>-251.6722006160001</v>
+        <v>-257.5046313920001</v>
       </c>
       <c r="Q93">
-        <v>-193.4722006160001</v>
+        <v>-199.3046313920001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8216288274283511</v>
+        <v>0.9186074308568952</v>
       </c>
       <c r="T93">
-        <v>9.294229440537514</v>
+        <v>10.45600812060471</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1419710966504565</v>
+        <v>0.1404279325564299</v>
       </c>
       <c r="W93">
-        <v>0.1722922037925883</v>
+        <v>0.1726020711426689</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5258188764831724</v>
+        <v>0.5201034539127031</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9099,22 +9099,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.232282499919807</v>
+        <v>0.233832499919807</v>
       </c>
       <c r="C94">
-        <v>-1918.243033441908</v>
+        <v>-1971.351856872608</v>
       </c>
       <c r="D94">
-        <v>1615.844966558093</v>
+        <v>1602.525143127392</v>
       </c>
       <c r="E94">
-        <v>2668.188</v>
+        <v>2707.977</v>
       </c>
       <c r="F94">
-        <v>3660.588</v>
+        <v>3700.377</v>
       </c>
       <c r="G94">
         <v>126.5</v>
@@ -9135,37 +9135,37 @@
         <v>382.3</v>
       </c>
       <c r="M94">
-        <v>735.0460704000001</v>
+        <v>743.0357016000002</v>
       </c>
       <c r="N94">
-        <v>-352.7460704000001</v>
+        <v>-360.7357016000002</v>
       </c>
       <c r="O94">
-        <v>-95.24143900800004</v>
+        <v>-97.39863943200005</v>
       </c>
       <c r="P94">
-        <v>-257.5046313920001</v>
+        <v>-263.3370621680002</v>
       </c>
       <c r="Q94">
-        <v>-199.3046313920001</v>
+        <v>-205.1370621680002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9186074308568952</v>
+        <v>1.043294206693595</v>
       </c>
       <c r="T94">
-        <v>10.45600812060471</v>
+        <v>11.94972356640538</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1404279325564299</v>
+        <v>0.1389179547870059</v>
       </c>
       <c r="W94">
-        <v>0.1726020711426689</v>
+        <v>0.1729052746787692</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5201034539127031</v>
+        <v>0.5145109436555773</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9181,22 +9181,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.233832499919807</v>
+        <v>0.235382499919807</v>
       </c>
       <c r="C95">
-        <v>-1971.351856872608</v>
+        <v>-2024.242878277</v>
       </c>
       <c r="D95">
-        <v>1602.525143127392</v>
+        <v>1589.423121723</v>
       </c>
       <c r="E95">
-        <v>2707.977</v>
+        <v>2747.766</v>
       </c>
       <c r="F95">
-        <v>3700.377</v>
+        <v>3740.166</v>
       </c>
       <c r="G95">
         <v>126.5</v>
@@ -9217,37 +9217,37 @@
         <v>382.3</v>
       </c>
       <c r="M95">
-        <v>743.0357016000002</v>
+        <v>751.0253328</v>
       </c>
       <c r="N95">
-        <v>-360.7357016000002</v>
+        <v>-368.7253328</v>
       </c>
       <c r="O95">
-        <v>-97.39863943200005</v>
+        <v>-99.55583985600002</v>
       </c>
       <c r="P95">
-        <v>-263.3370621680002</v>
+        <v>-269.169492944</v>
       </c>
       <c r="Q95">
-        <v>-205.1370621680002</v>
+        <v>-210.969492944</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.043294206693595</v>
+        <v>1.209543241142528</v>
       </c>
       <c r="T95">
-        <v>11.94972356640538</v>
+        <v>13.94134416080628</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1389179547870059</v>
+        <v>0.1374401042041654</v>
       </c>
       <c r="W95">
-        <v>0.1729052746787692</v>
+        <v>0.1732020270758036</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5145109436555773</v>
+        <v>0.5090374229783903</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9263,22 +9263,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.235382499919807</v>
+        <v>0.236932499919807</v>
       </c>
       <c r="C96">
-        <v>-2024.242878277</v>
+        <v>-2076.921396489258</v>
       </c>
       <c r="D96">
-        <v>1589.423121723</v>
+        <v>1576.533603510743</v>
       </c>
       <c r="E96">
-        <v>2747.766</v>
+        <v>2787.555</v>
       </c>
       <c r="F96">
-        <v>3740.166</v>
+        <v>3779.955</v>
       </c>
       <c r="G96">
         <v>126.5</v>
@@ -9299,37 +9299,37 @@
         <v>382.3</v>
       </c>
       <c r="M96">
-        <v>751.0253328</v>
+        <v>759.0149640000001</v>
       </c>
       <c r="N96">
-        <v>-368.7253328</v>
+        <v>-376.7149640000001</v>
       </c>
       <c r="O96">
-        <v>-99.55583985600002</v>
+        <v>-101.71304028</v>
       </c>
       <c r="P96">
-        <v>-269.169492944</v>
+        <v>-275.0019237200001</v>
       </c>
       <c r="Q96">
-        <v>-210.969492944</v>
+        <v>-216.8019237200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.209543241142528</v>
+        <v>1.442291889371033</v>
       </c>
       <c r="T96">
-        <v>13.94134416080628</v>
+        <v>16.72961299296754</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1374401042041654</v>
+        <v>0.1359933662651742</v>
       </c>
       <c r="W96">
-        <v>0.1732020270758036</v>
+        <v>0.173492532053953</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5090374229783903</v>
+        <v>0.5036791343154599</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9345,22 +9345,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.236932499919807</v>
+        <v>0.2736201320012811</v>
       </c>
       <c r="C97">
-        <v>-2076.921396489258</v>
+        <v>-2370.591755882718</v>
       </c>
       <c r="D97">
-        <v>1576.533603510743</v>
+        <v>1322.652244117283</v>
       </c>
       <c r="E97">
-        <v>2787.555</v>
+        <v>2827.344000000001</v>
       </c>
       <c r="F97">
-        <v>3779.955</v>
+        <v>3819.744000000001</v>
       </c>
       <c r="G97">
         <v>126.5</v>
@@ -9381,45 +9381,45 @@
         <v>382.3</v>
       </c>
       <c r="M97">
-        <v>759.0149640000001</v>
+        <v>900.6956352000002</v>
       </c>
       <c r="N97">
-        <v>-376.7149640000001</v>
+        <v>-518.3956352000002</v>
       </c>
       <c r="O97">
-        <v>-101.71304028</v>
+        <v>-139.9668215040001</v>
       </c>
       <c r="P97">
-        <v>-275.0019237200001</v>
+        <v>-378.4288136960001</v>
       </c>
       <c r="Q97">
-        <v>-216.8019237200001</v>
+        <v>-320.2288136960001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.442291889371033</v>
+        <v>1.829855663750645</v>
       </c>
       <c r="T97">
-        <v>16.72961299296754</v>
+        <v>21.37252714435938</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1359933662651742</v>
+        <v>0.1146014213525968</v>
       </c>
       <c r="W97">
-        <v>0.173492532053953</v>
+        <v>0.2087769848450577</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5036791343154599</v>
+        <v>0.4244497087133212</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9427,22 +9427,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.273620132001281</v>
+        <v>0.275520132001281</v>
       </c>
       <c r="C98">
-        <v>-2370.591755882717</v>
+        <v>-2421.320325009418</v>
       </c>
       <c r="D98">
-        <v>1322.652244117283</v>
+        <v>1311.712674990583</v>
       </c>
       <c r="E98">
-        <v>2827.344</v>
+        <v>2867.133</v>
       </c>
       <c r="F98">
-        <v>3819.744</v>
+        <v>3859.533</v>
       </c>
       <c r="G98">
         <v>126.5</v>
@@ -9463,37 +9463,37 @@
         <v>382.3</v>
       </c>
       <c r="M98">
-        <v>900.6956352000001</v>
+        <v>910.0778814</v>
       </c>
       <c r="N98">
-        <v>-518.3956352000001</v>
+        <v>-527.7778814000001</v>
       </c>
       <c r="O98">
-        <v>-139.9668215040001</v>
+        <v>-142.500027978</v>
       </c>
       <c r="P98">
-        <v>-378.4288136960001</v>
+        <v>-385.277853422</v>
       </c>
       <c r="Q98">
-        <v>-320.2288136960001</v>
+        <v>-327.077853422</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.82985566375064</v>
+        <v>2.424540885000853</v>
       </c>
       <c r="T98">
-        <v>21.37252714435932</v>
+        <v>28.49670285914576</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1146014213525968</v>
+        <v>0.1134199634005081</v>
       </c>
       <c r="W98">
-        <v>0.2087769848450577</v>
+        <v>0.2090555726301602</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4244497087133213</v>
+        <v>0.4200739385204005</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9509,22 +9509,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.275520132001281</v>
+        <v>0.2774201320012811</v>
       </c>
       <c r="C99">
-        <v>-2421.320325009418</v>
+        <v>-2471.869417670398</v>
       </c>
       <c r="D99">
-        <v>1311.712674990583</v>
+        <v>1300.952582329603</v>
       </c>
       <c r="E99">
-        <v>2867.133</v>
+        <v>2906.922</v>
       </c>
       <c r="F99">
-        <v>3859.533</v>
+        <v>3899.322</v>
       </c>
       <c r="G99">
         <v>126.5</v>
@@ -9545,37 +9545,37 @@
         <v>382.3</v>
       </c>
       <c r="M99">
-        <v>910.0778814</v>
+        <v>919.4601276000001</v>
       </c>
       <c r="N99">
-        <v>-527.7778814000001</v>
+        <v>-537.1601276000001</v>
       </c>
       <c r="O99">
-        <v>-142.500027978</v>
+        <v>-145.033234452</v>
       </c>
       <c r="P99">
-        <v>-385.277853422</v>
+        <v>-392.1268931480001</v>
       </c>
       <c r="Q99">
-        <v>-327.077853422</v>
+        <v>-333.9268931480001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.424540885000853</v>
+        <v>3.613911327501281</v>
       </c>
       <c r="T99">
-        <v>28.49670285914576</v>
+        <v>42.74505428871864</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1134199634005081</v>
+        <v>0.1122626168351968</v>
       </c>
       <c r="W99">
-        <v>0.2090555726301602</v>
+        <v>0.2093284749502606</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4200739385204005</v>
+        <v>0.4157874697599883</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9591,22 +9591,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2774201320012811</v>
+        <v>0.279320132001281</v>
       </c>
       <c r="C100">
-        <v>-2471.869417670398</v>
+        <v>-2522.243414712163</v>
       </c>
       <c r="D100">
-        <v>1300.952582329603</v>
+        <v>1290.367585287837</v>
       </c>
       <c r="E100">
-        <v>2906.922</v>
+        <v>2946.711</v>
       </c>
       <c r="F100">
-        <v>3899.322</v>
+        <v>3939.111</v>
       </c>
       <c r="G100">
         <v>126.5</v>
@@ -9627,37 +9627,37 @@
         <v>382.3</v>
       </c>
       <c r="M100">
-        <v>919.4601276000001</v>
+        <v>928.8423738</v>
       </c>
       <c r="N100">
-        <v>-537.1601276000001</v>
+        <v>-546.5423738000001</v>
       </c>
       <c r="O100">
-        <v>-145.033234452</v>
+        <v>-147.566440926</v>
       </c>
       <c r="P100">
-        <v>-392.1268931480001</v>
+        <v>-398.975932874</v>
       </c>
       <c r="Q100">
-        <v>-333.9268931480001</v>
+        <v>-340.775932874</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.613911327501281</v>
+        <v>7.182022655002561</v>
       </c>
       <c r="T100">
-        <v>42.74505428871864</v>
+        <v>85.49010857743727</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1122626168351968</v>
+        <v>0.1111286510085787</v>
       </c>
       <c r="W100">
-        <v>0.2093284749502606</v>
+        <v>0.2095958640921771</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9665,91 +9665,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4157874697599883</v>
+        <v>0.4115875963280692</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.279320132001281</v>
-      </c>
-      <c r="C101">
-        <v>-2522.243414712163</v>
-      </c>
-      <c r="D101">
-        <v>1290.367585287837</v>
-      </c>
-      <c r="E101">
-        <v>2946.711</v>
-      </c>
-      <c r="F101">
-        <v>3939.111</v>
-      </c>
-      <c r="G101">
-        <v>126.5</v>
-      </c>
-      <c r="H101">
-        <v>2986.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>440.4999999999999</v>
-      </c>
-      <c r="K101">
-        <v>58.19999999999999</v>
-      </c>
-      <c r="L101">
-        <v>382.3</v>
-      </c>
-      <c r="M101">
-        <v>928.8423738</v>
-      </c>
-      <c r="N101">
-        <v>-546.5423738000001</v>
-      </c>
-      <c r="O101">
-        <v>-147.566440926</v>
-      </c>
-      <c r="P101">
-        <v>-398.975932874</v>
-      </c>
-      <c r="Q101">
-        <v>-340.775932874</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.182022655002561</v>
-      </c>
-      <c r="T101">
-        <v>85.49010857743727</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1111286510085787</v>
-      </c>
-      <c r="W101">
-        <v>0.2095958640921771</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4115875963280692</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
